--- a/results/exp01-svhn-vgg11-e8-zerofill/20260921-213234/rounds.xlsx
+++ b/results/exp01-svhn-vgg11-e8-zerofill/20260921-213234/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2112,6 +2112,6729 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:53:50</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6701792000428569</v>
+      </c>
+      <c r="F21" t="n">
+        <v>92.78964351567302</v>
+      </c>
+      <c r="G21" t="n">
+        <v>92.78964351567302</v>
+      </c>
+      <c r="H21" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" t="n">
+        <v>64.2976</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1:04.30</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>61.6698</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.5012</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1275.8088</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>21:15.81</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>0,2,1,9,7,6,3,5,4,8</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0:28;2:41;1:40;9:17;7:43;6:68;3:18;5:10;4:59;8:50</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0:[0,3];2:[0,3,4,7];1:[0,2,3,6];9:[2];7:[0,2,3,7];6:[0,1,3,4,5,6];3:[3];5:[4];4:[0,1,2,3,6];8:[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>c0:bw=28,experts=[0,3]; c2:bw=41,experts=[0,3,4,7]; c1:bw=40,experts=[0,2,3,6]; c9:bw=17,experts=[2]; c7:bw=43,experts=[0,2,3,7]; c6:bw=68,experts=[0,1,3,4,5,6]; c3:bw=18,experts=[3]; c5:bw=10,experts=[4]; c4:bw=59,experts=[0,1,2,3,6]; c8:bw=50,experts=[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>4.2736,8.0274,10.9659,3.0498,12.3948,9.4566,1.2986,2.2261,7.2397,2.7375</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:54:54</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.6720587880739756</v>
+      </c>
+      <c r="F22" t="n">
+        <v>93.26982175783651</v>
+      </c>
+      <c r="G22" t="n">
+        <v>93.26982175783651</v>
+      </c>
+      <c r="H22" t="n">
+        <v>21</v>
+      </c>
+      <c r="I22" t="n">
+        <v>63.8892</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1:03.89</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>61.2314</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.5206</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1339.714</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>22:19.71</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1,2,7,4,8,5,0,3,6,9</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1:41;2:39;7:12;4:48;8:18;5:32;0:66;3:10;6:16;9:25</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1:[0,3,6,7];2:[0,3,7];7:[3];4:[0,3,6,7];8:[3];5:[0,3,5];0:[0,1,2,3,6,7];3:[4];6:[3];9:[1,3]</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>c1:bw=41,experts=[0,3,6,7]; c2:bw=39,experts=[0,3,7]; c7:bw=12,experts=[3]; c4:bw=48,experts=[0,3,6,7]; c8:bw=18,experts=[3]; c5:bw=32,experts=[0,3,5]; c0:bw=66,experts=[0,1,2,3,6,7]; c3:bw=10,experts=[4]; c6:bw=16,experts=[3]; c9:bw=25,experts=[1,3]</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>10.9506,7.9381,12.2569,7.2536,2.6725,2.2473,4.2574,1.2617,9.3410,3.0522</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:55:58</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6657036820254515</v>
+      </c>
+      <c r="F23" t="n">
+        <v>93.03549477566072</v>
+      </c>
+      <c r="G23" t="n">
+        <v>93.26982175783651</v>
+      </c>
+      <c r="H23" t="n">
+        <v>21</v>
+      </c>
+      <c r="I23" t="n">
+        <v>63.7568</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1:03.76</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>61.1695</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.4497</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1403.488</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>23:23.49</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>7,9,1,6,5,2,0,4,3,8</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>7:16;9:33;1:10;6:61;5:17;2:66;0:67;4:36;3:56;8:33</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>7:[1];9:[0,3,4];1:[3];6:[0,2,3,4,6,7];5:[1];2:[0,1,2,3,4,7];0:[0,2,3,4,6,7];4:[0,3,6];3:[0,1,2,3,6];8:[0,3,4]</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>c7:bw=16,experts=[1]; c9:bw=33,experts=[0,3,4]; c1:bw=10,experts=[3]; c6:bw=61,experts=[0,2,3,4,6,7]; c5:bw=17,experts=[1]; c2:bw=66,experts=[0,1,2,3,4,7]; c0:bw=67,experts=[0,2,3,4,6,7]; c4:bw=36,experts=[0,3,6]; c3:bw=56,experts=[0,1,2,3,6]; c8:bw=33,experts=[0,3,4]</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>12.1738,3.0890,10.7929,9.4514,2.2327,7.9987,4.2144,7.2172,1.3080,2.6913</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:57:02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6913954594812123</v>
+      </c>
+      <c r="F24" t="n">
+        <v>92.98171481253841</v>
+      </c>
+      <c r="G24" t="n">
+        <v>93.26982175783651</v>
+      </c>
+      <c r="H24" t="n">
+        <v>21</v>
+      </c>
+      <c r="I24" t="n">
+        <v>64.0154</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1:04.02</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>61.3948</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.4833</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1467.7241</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>24:27.72</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5,7,4,6,9,8,3,1,2,0</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>5:52;7:15;4:56;6:10;9:50;8:35;3:15;1:62;2:32;0:11</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>5:[0,2,3,6,7];7:[6];4:[0,2,3,6,7];6:[3];9:[0,2,3,6,7];8:[0,1,3];3:[3];1:[0,1,2,3,6,7];2:[0,2,3];0:[3]</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>c5:bw=52,experts=[0,2,3,6,7]; c7:bw=15,experts=[6]; c4:bw=56,experts=[0,2,3,6,7]; c6:bw=10,experts=[3]; c9:bw=50,experts=[0,2,3,6,7]; c8:bw=35,experts=[0,1,3]; c3:bw=15,experts=[3]; c1:bw=62,experts=[0,1,2,3,6,7]; c2:bw=32,experts=[0,2,3]; c0:bw=11,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2.2835,12.0966,7.4094,9.3982,3.0820,2.7923,1.3063,10.8733,7.9708,4.1824</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:58:06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7199108006779873</v>
+      </c>
+      <c r="F25" t="n">
+        <v>87.69207129686539</v>
+      </c>
+      <c r="G25" t="n">
+        <v>93.26982175783651</v>
+      </c>
+      <c r="H25" t="n">
+        <v>21</v>
+      </c>
+      <c r="I25" t="n">
+        <v>63.4127</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1:03.41</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>60.7867</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.4925</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1531.1532</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>25:31.15</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>6,4,7,9,2,1,5,8,3,0</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>6:30;4:12;7:10;9:50;2:43;1:10;5:25;8:18;3:10;0:31</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>6:[2,3,6];4:[4];7:[3];9:[0,2,3,6,7];2:[0,3,5,6];1:[4];5:[0,3];8:[3];3:[3];0:[0,3,5]</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>c6:bw=30,experts=[2,3,6]; c4:bw=12,experts=[4]; c7:bw=10,experts=[3]; c9:bw=50,experts=[0,2,3,6,7]; c2:bw=43,experts=[0,3,5,6]; c1:bw=10,experts=[4]; c5:bw=25,experts=[0,3]; c8:bw=18,experts=[3]; c3:bw=10,experts=[3]; c0:bw=31,experts=[0,3,5]</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>9.4292,7.2053,12.2674,3.0911,7.9706,10.3518,2.2759,2.6745,1.2899,4.2309</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:59:10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7309588417181686</v>
+      </c>
+      <c r="F26" t="n">
+        <v>93.76920712968654</v>
+      </c>
+      <c r="G26" t="n">
+        <v>93.76920712968654</v>
+      </c>
+      <c r="H26" t="n">
+        <v>25</v>
+      </c>
+      <c r="I26" t="n">
+        <v>64.3584</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1:04.36</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>61.7505</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.4795</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1595.5295</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>26:35.53</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>9,6,4,3,5,1,8,2,0,7</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>9:40;6:16;4:58;3:14;5:64;1:49;8:55;2:12;0:56;7:40</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>9:[0,3,5,6];6:[3];4:[0,2,3,5,7];3:[5];5:[0,1,2,3,6,7];1:[0,2,3,5];8:[0,2,3,5,6];2:[3];0:[0,2,3,6,7];7:[0,3,5,7]</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>c9:bw=40,experts=[0,3,5,6]; c6:bw=16,experts=[3]; c4:bw=58,experts=[0,2,3,5,7]; c3:bw=14,experts=[5]; c5:bw=64,experts=[0,1,2,3,6,7]; c1:bw=49,experts=[0,2,3,5]; c8:bw=55,experts=[0,2,3,5,6]; c2:bw=12,experts=[3]; c0:bw=56,experts=[0,2,3,6,7]; c7:bw=40,experts=[0,3,5,7]</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>3.1185,9.4378,7.3503,1.2670,2.3028,10.9102,2.6980,7.8940,4.2563,12.5157</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:00:14</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6497123202727362</v>
+      </c>
+      <c r="F27" t="n">
+        <v>93.52335586969883</v>
+      </c>
+      <c r="G27" t="n">
+        <v>93.76920712968654</v>
+      </c>
+      <c r="H27" t="n">
+        <v>25</v>
+      </c>
+      <c r="I27" t="n">
+        <v>64.376</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1:04.38</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>61.7525</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.4814</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1659.9231</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>27:39.92</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3,6,9,7,1,5,2,8,0,4</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3:44;6:34;9:50;7:31;1:33;5:20;2:30;8:53;0:11;4:48</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>3:[2,3,6,7];6:[0,3,6];9:[0,1,2,3,6];7:[0,3,4];1:[0,3,6];5:[0,3];2:[0,3,6];8:[0,1,2,3,6];0:[3];4:[0,2,3,6]</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>c3:bw=44,experts=[2,3,6,7]; c6:bw=34,experts=[0,3,6]; c9:bw=50,experts=[0,1,2,3,6]; c7:bw=31,experts=[0,3,4]; c1:bw=33,experts=[0,3,6]; c5:bw=20,experts=[0,3]; c2:bw=30,experts=[0,3,6]; c8:bw=53,experts=[0,1,2,3,6]; c0:bw=11,experts=[3]; c4:bw=48,experts=[0,2,3,6]</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1.3163,9.4429,3.0775,12.4638,10.9444,2.2749,7.9755,2.7286,4.2118,7.3167</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:01:19</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6421633913387228</v>
+      </c>
+      <c r="F28" t="n">
+        <v>93.54640442532268</v>
+      </c>
+      <c r="G28" t="n">
+        <v>93.76920712968654</v>
+      </c>
+      <c r="H28" t="n">
+        <v>25</v>
+      </c>
+      <c r="I28" t="n">
+        <v>64.3413</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1:04.34</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>61.7492</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.4603</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1724.2827</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>28:44.28</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>7,1,4,0,9,2,8,3,6,5</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>7:51;1:62;4:12;0:36;9:18;2:20;8:55;3:21;6:63;5:37</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>7:[0,2,3,4,7];1:[0,1,2,3,6,7];4:[3];0:[0,3,7];9:[3];2:[0,3];8:[0,2,3,6,7];3:[3,6];6:[0,1,2,3,4,7];5:[0,3,6]</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>c7:bw=51,experts=[0,2,3,4,7]; c1:bw=62,experts=[0,1,2,3,6,7]; c4:bw=12,experts=[3]; c0:bw=36,experts=[0,3,7]; c9:bw=18,experts=[3]; c2:bw=20,experts=[0,3]; c8:bw=55,experts=[0,2,3,6,7]; c3:bw=21,experts=[3,6]; c6:bw=63,experts=[0,1,2,3,4,7]; c5:bw=37,experts=[0,3,6]</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>12.5645,10.9947,7.2551,4.2256,3.0396,7.9004,2.7110,1.2931,9.5150,2.2502</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:02:23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6472114568489152</v>
+      </c>
+      <c r="F29" t="n">
+        <v>93.73847572218807</v>
+      </c>
+      <c r="G29" t="n">
+        <v>93.76920712968654</v>
+      </c>
+      <c r="H29" t="n">
+        <v>25</v>
+      </c>
+      <c r="I29" t="n">
+        <v>64.1086</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1:04.11</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>61.4319</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.5522</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1788.412</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>29:48.41</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>6,9,0,8,2,5,1,3,4,7</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>6:29;9:49;0:47;8:29;2:10;5:33;1:25;3:12;4:10;7:10</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>6:[3,5];9:[0,2,3,6];0:[0,3,6,7];8:[0,3];2:[3];5:[0,3,4];1:[0,3];3:[3];4:[1];7:[3]</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>c6:bw=29,experts=[3,5]; c9:bw=49,experts=[0,2,3,6]; c0:bw=47,experts=[0,3,6,7]; c8:bw=29,experts=[0,3]; c2:bw=10,experts=[3]; c5:bw=33,experts=[0,3,4]; c1:bw=25,experts=[0,3]; c3:bw=12,experts=[3]; c4:bw=10,experts=[1]; c7:bw=10,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>9.4396,3.1132,4.2969,2.6989,7.9156,2.2413,10.8459,1.2982,7.2072,12.3750</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:03:27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6414650946197054</v>
+      </c>
+      <c r="F30" t="n">
+        <v>94.12261831591887</v>
+      </c>
+      <c r="G30" t="n">
+        <v>94.12261831591887</v>
+      </c>
+      <c r="H30" t="n">
+        <v>29</v>
+      </c>
+      <c r="I30" t="n">
+        <v>64.19289999999999</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1:04.19</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>61.5469</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.5095</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1852.6236</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>30:52.62</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>4,0,1,9,6,8,7,3,2,5</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>4:38;0:44;1:33;9:44;6:43;8:34;7:21;3:32;2:18;5:33</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4:[0,2,3];0:[0,1,3,7];1:[0,3,6];9:[0,2,3,6];6:[0,3,4,7];8:[0,3,6];7:[0,3];3:[3,4,6];2:[3];5:[0,3,5]</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>c4:bw=38,experts=[0,2,3]; c0:bw=44,experts=[0,1,3,7]; c1:bw=33,experts=[0,3,6]; c9:bw=44,experts=[0,2,3,6]; c6:bw=43,experts=[0,3,4,7]; c8:bw=34,experts=[0,3,6]; c7:bw=21,experts=[0,3]; c3:bw=32,experts=[3,4,6]; c2:bw=18,experts=[3]; c5:bw=33,experts=[0,3,5]</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>7.2809,4.2263,10.8876,3.0628,9.4057,2.7174,12.4387,1.3237,7.9433,2.2606</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:04:31</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6483766431008436</v>
+      </c>
+      <c r="F31" t="n">
+        <v>91.87154271665642</v>
+      </c>
+      <c r="G31" t="n">
+        <v>94.12261831591887</v>
+      </c>
+      <c r="H31" t="n">
+        <v>29</v>
+      </c>
+      <c r="I31" t="n">
+        <v>63.8403</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1:03.84</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>61.2694</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.4428</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1916.4833</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>31:56.48</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5,1,9,4,0,8,6,7,3,2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>5:62;1:35;9:54;4:51;0:17;8:41;6:11;7:12;3:59;2:27</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>5:[0,1,2,3,6,7];1:[0,3,6];9:[0,1,3,4,6];4:[0,2,3,6,7];0:[4];8:[0,3,4,6];6:[3];7:[1];3:[0,1,2,3,6];2:[1,4]</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>c5:bw=62,experts=[0,1,2,3,6,7]; c1:bw=35,experts=[0,3,6]; c9:bw=54,experts=[0,1,3,4,6]; c4:bw=51,experts=[0,2,3,6,7]; c0:bw=17,experts=[4]; c8:bw=41,experts=[0,3,4,6]; c6:bw=11,experts=[3]; c7:bw=12,experts=[1]; c3:bw=59,experts=[0,1,2,3,6]; c2:bw=27,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2.2959,10.8965,3.0811,7.3554,4.1263,2.7158,9.3771,12.1739,1.3067,7.9408</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:05:35</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7409334994253771</v>
+      </c>
+      <c r="F32" t="n">
+        <v>93.84219422249539</v>
+      </c>
+      <c r="G32" t="n">
+        <v>94.12261831591887</v>
+      </c>
+      <c r="H32" t="n">
+        <v>29</v>
+      </c>
+      <c r="I32" t="n">
+        <v>64.4769</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1:04.48</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>61.8968</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.4448</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1980.979</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>33:00.98</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>6,4,9,1,5,8,3,2,0,7</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>6:29;4:19;9:45;1:30;5:62;8:33;3:24;2:15;0:47;7:63</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>6:[3,4];4:[3];9:[0,2,3,6];1:[0,3,6];5:[0,2,3,4,6,7];8:[0,3,6];3:[3,6];2:[7];0:[0,3,6,7];7:[0,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>c6:bw=29,experts=[3,4]; c4:bw=19,experts=[3]; c9:bw=45,experts=[0,2,3,6]; c1:bw=30,experts=[0,3,6]; c5:bw=62,experts=[0,2,3,4,6,7]; c8:bw=33,experts=[0,3,6]; c3:bw=24,experts=[3,6]; c2:bw=15,experts=[7]; c0:bw=47,experts=[0,3,6,7]; c7:bw=63,experts=[0,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>9.4687,7.2929,3.0994,10.9134,2.3112,2.7532,1.3103,7.9857,4.2481,12.5138</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:06:39</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.646526524875478</v>
+      </c>
+      <c r="F33" t="n">
+        <v>94.09572833435772</v>
+      </c>
+      <c r="G33" t="n">
+        <v>94.12261831591887</v>
+      </c>
+      <c r="H33" t="n">
+        <v>29</v>
+      </c>
+      <c r="I33" t="n">
+        <v>64.0433</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1:04.04</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>61.4847</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.4324</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2045.0416</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>34:05.04</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>8,5,4,7,0,1,3,6,2,9</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>8:21;5:36;4:49;7:47;0:46;1:21;3:28;6:27;2:54;9:31</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>8:[0,3];5:[0,3,6];4:[0,3,4,7];7:[0,3,4,7];0:[0,3,5,6];1:[3,4];3:[3,6];6:[3,4];2:[0,2,3,5,6];9:[0,3,7]</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>c8:bw=21,experts=[0,3]; c5:bw=36,experts=[0,3,6]; c4:bw=49,experts=[0,3,4,7]; c7:bw=47,experts=[0,3,4,7]; c0:bw=46,experts=[0,3,5,6]; c1:bw=21,experts=[3,4]; c3:bw=28,experts=[3,6]; c6:bw=27,experts=[3,4]; c2:bw=54,experts=[0,2,3,5,6]; c9:bw=31,experts=[0,3,7]</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2.7204,2.2819,7.2962,12.4159,4.2678,10.7865,1.3119,9.3320,8.0115,3.0605</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:07:44</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6365223913120133</v>
+      </c>
+      <c r="F34" t="n">
+        <v>94.12645974185618</v>
+      </c>
+      <c r="G34" t="n">
+        <v>94.12645974185618</v>
+      </c>
+      <c r="H34" t="n">
+        <v>33</v>
+      </c>
+      <c r="I34" t="n">
+        <v>64.3006</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1:04.30</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>61.6813</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.1251</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.491</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2109.3619</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>35:09.36</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>7,1,3,6,5,9,2,8,4,0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>7:52;1:34;3:70;6:37;5:29;9:42;2:24;8:50;4:45;0:62</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>7:[0,3,4,5,7];1:[0,3,5];3:[0,1,2,3,4,5,6];6:[1,3,4];5:[0,3];9:[0,3,5,6];2:[0,3];8:[0,2,3,5,6];4:[0,2,3,5];0:[0,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>c7:bw=52,experts=[0,3,4,5,7]; c1:bw=34,experts=[0,3,5]; c3:bw=70,experts=[0,1,2,3,4,5,6]; c6:bw=37,experts=[1,3,4]; c5:bw=29,experts=[0,3]; c9:bw=42,experts=[0,3,5,6]; c2:bw=24,experts=[0,3]; c8:bw=50,experts=[0,2,3,5,6]; c4:bw=45,experts=[0,2,3,5]; c0:bw=62,experts=[0,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>12.5132,10.8400,1.3308,9.4897,2.2496,3.0774,7.9505,2.7175,7.2741,4.2387</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:08:48</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.629718893506001</v>
+      </c>
+      <c r="F35" t="n">
+        <v>94.35310387215735</v>
+      </c>
+      <c r="G35" t="n">
+        <v>94.35310387215735</v>
+      </c>
+      <c r="H35" t="n">
+        <v>34</v>
+      </c>
+      <c r="I35" t="n">
+        <v>64.5318</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1:04.53</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>61.8804</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.5138</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2173.9136</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>36:13.91</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>4,1,6,9,8,0,5,7,3,2</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>4:46;1:46;6:48;9:68;8:42;0:22;5:60;7:32;3:72;2:54</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>4:[0,2,3,6];1:[0,2,3,6];6:[1,3,4,6];9:[0,1,2,3,4,6];8:[0,1,3,6];0:[0,3];5:[0,1,2,3,6,7];7:[0,3,4];3:[0,1,2,3,4,6,7];2:[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>c4:bw=46,experts=[0,2,3,6]; c1:bw=46,experts=[0,2,3,6]; c6:bw=48,experts=[1,3,4,6]; c9:bw=68,experts=[0,1,2,3,4,6]; c8:bw=42,experts=[0,1,3,6]; c0:bw=22,experts=[0,3]; c5:bw=60,experts=[0,1,2,3,6,7]; c7:bw=32,experts=[0,3,4]; c3:bw=72,experts=[0,1,2,3,4,6,7]; c2:bw=54,experts=[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>7.3329,10.9066,9.4917,3.1136,2.7156,4.2308,2.2649,12.4651,1.3205,8.0386</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:09:53</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6280969484562611</v>
+      </c>
+      <c r="F36" t="n">
+        <v>94.29932390903504</v>
+      </c>
+      <c r="G36" t="n">
+        <v>94.35310387215735</v>
+      </c>
+      <c r="H36" t="n">
+        <v>34</v>
+      </c>
+      <c r="I36" t="n">
+        <v>64.43859999999999</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1:04.44</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>61.8374</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.4703</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2238.373</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>37:18.37</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>4,0,1,6,2,8,9,7,5,3</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>4:33;0:20;1:31;6:44;2:46;8:50;9:27;7:48;5:41;3:24</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>4:[0,2,3];0:[0,3];1:[1,3,7];6:[1,2,3,4];2:[0,3,4,7];8:[0,2,3,6,7];9:[0,3];7:[0,3,4,7];5:[0,3,6,7];3:[3,6]</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>c4:bw=33,experts=[0,2,3]; c0:bw=20,experts=[0,3]; c1:bw=31,experts=[1,3,7]; c6:bw=44,experts=[1,2,3,4]; c2:bw=46,experts=[0,3,4,7]; c8:bw=50,experts=[0,2,3,6,7]; c9:bw=27,experts=[0,3]; c7:bw=48,experts=[0,3,4,7]; c5:bw=41,experts=[0,3,6,7]; c3:bw=24,experts=[3,6]</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>7.3539,4.2809,10.8821,9.5172,7.9942,2.6998,3.0636,12.4461,2.2858,1.3139</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:57</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6242547094014005</v>
+      </c>
+      <c r="F37" t="n">
+        <v>94.53365089121081</v>
+      </c>
+      <c r="G37" t="n">
+        <v>94.53365089121081</v>
+      </c>
+      <c r="H37" t="n">
+        <v>36</v>
+      </c>
+      <c r="I37" t="n">
+        <v>64.3135</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1:04.31</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>61.7147</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.4605</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2302.7072</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>38:22.71</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>9,0,3,7,6,5,1,4,8,2</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>9:37;0:36;3:60;7:27;6:43;5:49;1:10;4:74;8:51;2:50</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>9:[0,3,6];0:[0,3,7];3:[0,1,2,3,4,6];7:[3,7];6:[1,3,4,5];5:[0,3,6,7];1:[3];4:[0,1,2,3,4,6,7];8:[0,2,3,6,7];2:[0,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>c9:bw=37,experts=[0,3,6]; c0:bw=36,experts=[0,3,7]; c3:bw=60,experts=[0,1,2,3,4,6]; c7:bw=27,experts=[3,7]; c6:bw=43,experts=[1,3,4,5]; c5:bw=49,experts=[0,3,6,7]; c1:bw=10,experts=[3]; c4:bw=74,experts=[0,1,2,3,4,6,7]; c8:bw=51,experts=[0,2,3,6,7]; c2:bw=50,experts=[0,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>3.0942,4.2572,1.3296,12.4484,9.5454,2.2527,10.6284,7.3827,2.7262,8.0498</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:12:01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6222648392799515</v>
+      </c>
+      <c r="F38" t="n">
+        <v>94.55285802089736</v>
+      </c>
+      <c r="G38" t="n">
+        <v>94.55285802089736</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37</v>
+      </c>
+      <c r="I38" t="n">
+        <v>64.18899999999999</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1:04.19</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>61.564</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.4948</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2366.9171</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>39:26.92</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1,5,2,6,4,7,9,0,3,8</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1:18;5:39;2:36;6:65;4:39;7:42;9:40;0:54;3:36;8:10</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1:[3];5:[0,3,5];2:[0,3,4];6:[0,1,3,4,6,7];4:[0,3,7];7:[0,3,4,7];9:[0,1,3,6];0:[0,1,3,6,7];3:[2,3,6];8:[3]</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>c1:bw=18,experts=[3]; c5:bw=39,experts=[0,3,5]; c2:bw=36,experts=[0,3,4]; c6:bw=65,experts=[0,1,3,4,6,7]; c4:bw=39,experts=[0,3,7]; c7:bw=42,experts=[0,3,4,7]; c9:bw=40,experts=[0,1,3,6]; c0:bw=54,experts=[0,1,3,6,7]; c3:bw=36,experts=[2,3,6]; c8:bw=10,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>10.7546,2.2605,7.9565,9.5844,7.2373,12.4856,3.0756,4.2107,1.3024,2.6966</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:05</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6247562732282546</v>
+      </c>
+      <c r="F39" t="n">
+        <v>94.50676090964966</v>
+      </c>
+      <c r="G39" t="n">
+        <v>94.55285802089736</v>
+      </c>
+      <c r="H39" t="n">
+        <v>37</v>
+      </c>
+      <c r="I39" t="n">
+        <v>64.0397</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1:04.04</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>61.3986</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.1341</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2431.013</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>40:31.01</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>8,6,4,1,5,2,3,7,9,0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>8:46;6:17;4:52;1:31;5:10;2:10;3:38;7:51;9:26;0:40</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>8:[0,3,4,6];6:[3];4:[0,2,3,6,7];1:[0,3,6];5:[3];2:[1];3:[0,3,6];7:[0,1,3,4,7];9:[3,6];0:[0,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>c8:bw=46,experts=[0,3,4,6]; c6:bw=17,experts=[3]; c4:bw=52,experts=[0,2,3,6,7]; c1:bw=31,experts=[0,3,6]; c5:bw=10,experts=[3]; c2:bw=10,experts=[1]; c3:bw=38,experts=[0,3,6]; c7:bw=51,experts=[0,1,3,4,7]; c9:bw=26,experts=[3,6]; c0:bw=40,experts=[0,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2.6892,9.4309,7.3370,10.6827,2.2390,7.9579,1.3152,12.4626,3.0645,4.2195</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:09</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6267734827768272</v>
+      </c>
+      <c r="F40" t="n">
+        <v>94.74108789182544</v>
+      </c>
+      <c r="G40" t="n">
+        <v>94.74108789182544</v>
+      </c>
+      <c r="H40" t="n">
+        <v>39</v>
+      </c>
+      <c r="I40" t="n">
+        <v>63.8521</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1:03.85</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>61.2224</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2.4989</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2494.8862</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>41:34.89</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3,0,1,7,6,8,2,4,9,5</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3:26;0:10;1:45;7:40;6:31;8:45;2:36;4:36;9:24;5:75</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3:[3,6];0:[3];1:[0,3,6,7];7:[0,2,3,6];6:[1,3,4];8:[0,2,3,6];2:[0,3,7];4:[0,3,7];9:[0,3];5:[0,1,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>c3:bw=26,experts=[3,6]; c0:bw=10,experts=[3]; c1:bw=45,experts=[0,3,6,7]; c7:bw=40,experts=[0,2,3,6]; c6:bw=31,experts=[1,3,4]; c8:bw=45,experts=[0,2,3,6]; c2:bw=36,experts=[0,3,7]; c4:bw=36,experts=[0,3,7]; c9:bw=24,experts=[0,3]; c5:bw=75,experts=[0,1,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1.3102,4.2373,10.6914,12.3437,9.4827,2.6787,7.9167,7.2575,3.0525,2.2516</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:15:14</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6191294873944919</v>
+      </c>
+      <c r="F41" t="n">
+        <v>94.52596803933621</v>
+      </c>
+      <c r="G41" t="n">
+        <v>94.74108789182544</v>
+      </c>
+      <c r="H41" t="n">
+        <v>39</v>
+      </c>
+      <c r="I41" t="n">
+        <v>64.372</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1:04.37</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>61.7788</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1268</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.4657</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2559.2795</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>42:39.28</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8,1,5,6,2,7,3,4,9,0</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>8:26;1:42;5:32;6:46;2:65;7:66;3:10;4:19;9:40;0:36</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8:[3,6];1:[0,3,4,6];5:[0,3,6];6:[1,3,4,6];2:[0,3,4,5,6,7];7:[0,2,3,4,6,7];3:[3];4:[3];9:[0,3,6,7];0:[0,3,5]</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>c8:bw=26,experts=[3,6]; c1:bw=42,experts=[0,3,4,6]; c5:bw=32,experts=[0,3,6]; c6:bw=46,experts=[1,3,4,6]; c2:bw=65,experts=[0,3,4,5,6,7]; c7:bw=66,experts=[0,2,3,4,6,7]; c3:bw=10,experts=[3]; c4:bw=19,experts=[3]; c9:bw=40,experts=[0,3,6,7]; c0:bw=36,experts=[0,3,5]</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2.6809,10.8431,2.2577,9.5609,8.0569,12.5380,1.3148,7.2174,3.0850,4.2242</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:16:18</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6211057138084354</v>
+      </c>
+      <c r="F42" t="n">
+        <v>93.82682851874615</v>
+      </c>
+      <c r="G42" t="n">
+        <v>94.74108789182544</v>
+      </c>
+      <c r="H42" t="n">
+        <v>39</v>
+      </c>
+      <c r="I42" t="n">
+        <v>64.086</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1:04.09</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>61.4894</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.4627</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2623.3868</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>43:43.39</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2,6,8,1,4,5,7,3,9,0</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2:54;6:10;8:57;1:10;4:50;5:61;7:68;3:40;9:54;0:10</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2:[0,2,3,4,7];6:[3];8:[0,3,5,6,7];1:[5];4:[0,3,5,6,7];5:[0,1,2,3,6,7];7:[0,3,4,5,6,7];3:[3,4,5,6];9:[0,1,3,5,6];0:[2]</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>c2:bw=54,experts=[0,2,3,4,7]; c6:bw=10,experts=[3]; c8:bw=57,experts=[0,3,5,6,7]; c1:bw=10,experts=[5]; c4:bw=50,experts=[0,3,5,6,7]; c5:bw=61,experts=[0,1,2,3,6,7]; c7:bw=68,experts=[0,3,4,5,6,7]; c3:bw=40,experts=[3,4,5,6]; c9:bw=54,experts=[0,1,3,5,6]; c0:bw=10,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>8.0543,9.4636,2.6950,10.6984,7.3038,2.2467,12.4663,1.3044,3.0929,4.1641</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:17:22</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6544015038396866</v>
+      </c>
+      <c r="F43" t="n">
+        <v>94.84480639213275</v>
+      </c>
+      <c r="G43" t="n">
+        <v>94.84480639213275</v>
+      </c>
+      <c r="H43" t="n">
+        <v>42</v>
+      </c>
+      <c r="I43" t="n">
+        <v>64.1232</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1:04.12</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>61.5451</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.1332</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2.4419</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2687.532</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>44:47.53</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5,1,3,9,6,0,7,4,8,2</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5:50;1:49;3:48;9:51;6:34;0:15;7:20;4:55;8:42;2:40</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5:[0,2,3,6,7];1:[0,2,3,6];3:[0,3,6,7];9:[0,2,3,4,6];6:[1,3,4];0:[4];7:[0,3];4:[0,1,2,3,6];8:[0,1,3,6];2:[0,3,4,7]</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>c5:bw=50,experts=[0,2,3,6,7]; c1:bw=49,experts=[0,2,3,6]; c3:bw=48,experts=[0,3,6,7]; c9:bw=51,experts=[0,2,3,4,6]; c6:bw=34,experts=[1,3,4]; c0:bw=15,experts=[4]; c7:bw=20,experts=[0,3]; c4:bw=55,experts=[0,1,2,3,6]; c8:bw=42,experts=[0,1,3,6]; c2:bw=40,experts=[0,3,4,7]</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2.2864,10.9477,1.3203,3.0910,9.4896,4.1028,12.2518,7.3211,2.7102,8.0243</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:18:26</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.6291396632084316</v>
+      </c>
+      <c r="F44" t="n">
+        <v>94.16871542716656</v>
+      </c>
+      <c r="G44" t="n">
+        <v>94.84480639213275</v>
+      </c>
+      <c r="H44" t="n">
+        <v>42</v>
+      </c>
+      <c r="I44" t="n">
+        <v>64.0496</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1:04.05</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>61.4573</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.1353</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2.4539</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2751.6041</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>45:51.60</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5,1,2,8,9,7,4,6,3,0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>5:53;1:58;2:51;8:45;9:32;7:21;4:34;6:12;3:65;0:21</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>5:[0,2,3,6,7];1:[0,1,2,3,6];2:[0,1,3,4,6];8:[0,2,3,6];9:[0,3,6];7:[0,3];4:[0,3,6];6:[2];3:[0,1,2,3,4,6];0:[0,3]</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>c5:bw=53,experts=[0,2,3,6,7]; c1:bw=58,experts=[0,1,2,3,6]; c2:bw=51,experts=[0,1,3,4,6]; c8:bw=45,experts=[0,2,3,6]; c9:bw=32,experts=[0,3,6]; c7:bw=21,experts=[0,3]; c4:bw=34,experts=[0,3,6]; c6:bw=12,experts=[2]; c3:bw=65,experts=[0,1,2,3,4,6]; c0:bw=21,experts=[0,3]</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2.2931,10.9359,8.0118,2.7138,3.0631,12.3276,7.3070,9.2238,1.3320,4.2491</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:19:31</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6259634713829837</v>
+      </c>
+      <c r="F45" t="n">
+        <v>94.64121081745544</v>
+      </c>
+      <c r="G45" t="n">
+        <v>94.84480639213275</v>
+      </c>
+      <c r="H45" t="n">
+        <v>42</v>
+      </c>
+      <c r="I45" t="n">
+        <v>64.48220000000001</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1:04.48</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>61.8515</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.4931</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2816.1091</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>46:56.11</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0,3,4,2,7,5,6,9,8,1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0:66;3:47;4:29;2:37;7:75;5:24;6:20;9:37;8:34;1:45</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0:[0,2,3,4,6,7];3:[0,2,3,6];4:[3,4];2:[0,3,4];7:[0,2,3,4,5,6,7];5:[0,3];6:[3,5];9:[0,3,6];8:[0,3,6];1:[0,2,3,6]</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>c0:bw=66,experts=[0,2,3,4,6,7]; c3:bw=47,experts=[0,2,3,6]; c4:bw=29,experts=[3,4]; c2:bw=37,experts=[0,3,4]; c7:bw=75,experts=[0,2,3,4,5,6,7]; c5:bw=24,experts=[0,3]; c6:bw=20,experts=[3,5]; c9:bw=37,experts=[0,3,6]; c8:bw=34,experts=[0,3,6]; c1:bw=45,experts=[0,2,3,6]</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>4.3091,1.3254,7.2862,7.9885,12.5071,2.2570,9.4477,3.0778,2.7114,10.9412</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:20:35</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6223501160545158</v>
+      </c>
+      <c r="F46" t="n">
+        <v>94.41840811309157</v>
+      </c>
+      <c r="G46" t="n">
+        <v>94.84480639213275</v>
+      </c>
+      <c r="H46" t="n">
+        <v>42</v>
+      </c>
+      <c r="I46" t="n">
+        <v>64.2085</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1:04.21</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>61.5494</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.5216</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2880.3402</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>48:00.34</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8,0,3,4,7,2,9,6,5,1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>8:55;0:36;3:67;4:64;7:36;2:49;9:25;6:10;5:44;1:56</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>8:[0,2,3,6,7];0:[0,1,3];3:[0,1,2,3,4,6];4:[0,2,3,4,6,7];7:[0,3,4];2:[0,2,3,7];9:[0,3];6:[0];5:[0,3,5,6];1:[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>c8:bw=55,experts=[0,2,3,6,7]; c0:bw=36,experts=[0,1,3]; c3:bw=67,experts=[0,1,2,3,4,6]; c4:bw=64,experts=[0,2,3,4,6,7]; c7:bw=36,experts=[0,3,4]; c2:bw=49,experts=[0,2,3,7]; c9:bw=25,experts=[0,3]; c6:bw=10,experts=[0]; c5:bw=44,experts=[0,3,5,6]; c1:bw=56,experts=[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2.7367,4.2520,1.3251,7.3310,12.3965,8.0768,3.0827,9.1987,2.2548,10.8951</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:21:39</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.6221300905662389</v>
+      </c>
+      <c r="F47" t="n">
+        <v>94.85633066994468</v>
+      </c>
+      <c r="G47" t="n">
+        <v>94.85633066994468</v>
+      </c>
+      <c r="H47" t="n">
+        <v>46</v>
+      </c>
+      <c r="I47" t="n">
+        <v>64.1814</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1:04.18</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>61.5747</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.4794</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2944.5445</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>49:04.54</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>9,3,6,1,4,5,2,8,0,7</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>9:37;3:27;6:39;1:41;4:64;5:41;2:57;8:39;0:55;7:28</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>9:[0,3,6];3:[3,6];6:[3,4,7];1:[0,2,3,6];4:[0,2,3,4,6,7];5:[0,2,3,6];2:[0,2,3,4,7];8:[0,3,4];0:[0,3,4,6,7];7:[1,3]</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>c9:bw=37,experts=[0,3,6]; c3:bw=27,experts=[3,6]; c6:bw=39,experts=[3,4,7]; c1:bw=41,experts=[0,2,3,6]; c4:bw=64,experts=[0,2,3,4,6,7]; c5:bw=41,experts=[0,2,3,6]; c2:bw=57,experts=[0,2,3,4,7]; c8:bw=39,experts=[0,3,4]; c0:bw=55,experts=[0,3,4,6,7]; c7:bw=28,experts=[1,3]</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>3.0806,1.3130,9.4623,10.8646,7.3649,2.2521,8.0010,2.6949,4.2757,12.2654</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:22:43</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.6152046528913262</v>
+      </c>
+      <c r="F48" t="n">
+        <v>94.91779348494161</v>
+      </c>
+      <c r="G48" t="n">
+        <v>94.91779348494161</v>
+      </c>
+      <c r="H48" t="n">
+        <v>47</v>
+      </c>
+      <c r="I48" t="n">
+        <v>64.3558</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1:04.36</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>61.7249</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.4959</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3008.9231</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>50:08.92</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>5,6,7,9,8,3,4,0,1,2</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>5:52;6:22;7:53;9:17;8:39;3:70;4:10;0:46;1:30;2:54</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>5:[0,3,4,6,7];6:[3,4];7:[0,2,3,4,7];9:[3];8:[0,3,6];3:[0,1,2,3,4,6,7];4:[3];0:[0,3,6,7];1:[0,3,6];2:[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>c5:bw=52,experts=[0,3,4,6,7]; c6:bw=22,experts=[3,4]; c7:bw=53,experts=[0,2,3,4,7]; c9:bw=17,experts=[3]; c8:bw=39,experts=[0,3,6]; c3:bw=70,experts=[0,1,2,3,4,6,7]; c4:bw=10,experts=[3]; c0:bw=46,experts=[0,3,6,7]; c1:bw=30,experts=[0,3,6]; c2:bw=54,experts=[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2.2795,9.4815,12.5326,3.0658,2.7156,1.3199,7.1762,4.2561,10.8756,8.0220</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:23:48</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6166755186782682</v>
+      </c>
+      <c r="F49" t="n">
+        <v>94.54133374308543</v>
+      </c>
+      <c r="G49" t="n">
+        <v>94.91779348494161</v>
+      </c>
+      <c r="H49" t="n">
+        <v>47</v>
+      </c>
+      <c r="I49" t="n">
+        <v>64.3715</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1:04.37</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>61.7144</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.1329</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.5213</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3073.3179</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>51:13.32</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1,8,4,2,9,6,5,7,0,3</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1:50;8:50;4:67;2:57;9:52;6:45;5:55;7:62;0:16;3:18</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1:[0,3,4,6,7];8:[0,2,3,6,7];4:[0,1,2,3,6,7];2:[0,3,4,5,7];9:[0,2,3,6,7];6:[3,4,5,6];5:[0,2,3,6,7];7:[0,2,3,4,6,7];0:[5];3:[3]</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>c1:bw=50,experts=[0,3,4,6,7]; c8:bw=50,experts=[0,2,3,6,7]; c4:bw=67,experts=[0,1,2,3,6,7]; c2:bw=57,experts=[0,3,4,5,7]; c9:bw=52,experts=[0,2,3,6,7]; c6:bw=45,experts=[3,4,5,6]; c5:bw=55,experts=[0,2,3,6,7]; c7:bw=62,experts=[0,2,3,4,6,7]; c0:bw=16,experts=[5]; c3:bw=18,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>10.9241,2.7159,7.3498,8.0225,3.0877,9.4710,2.2650,12.4080,4.1514,1.3191</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:24:52</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.6130548519660388</v>
+      </c>
+      <c r="F50" t="n">
+        <v>94.88706207744315</v>
+      </c>
+      <c r="G50" t="n">
+        <v>94.91779348494161</v>
+      </c>
+      <c r="H50" t="n">
+        <v>47</v>
+      </c>
+      <c r="I50" t="n">
+        <v>64.15770000000001</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1:04.16</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>61.5109</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.5228</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3137.5</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>52:17.50</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>4,3,8,0,2,5,6,7,9,1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>4:48;3:32;8:26;0:20;2:58;5:56;6:13;7:44;9:53;1:54</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>4:[0,3,5,7];3:[3,5,6];8:[3,5];0:[0,3];2:[0,2,3,4,7];5:[0,1,3,6,7];6:[3];7:[0,3,4,7];9:[0,1,3,5,6];1:[0,2,3,5,6]</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>c4:bw=48,experts=[0,3,5,7]; c3:bw=32,experts=[3,5,6]; c8:bw=26,experts=[3,5]; c0:bw=20,experts=[0,3]; c2:bw=58,experts=[0,2,3,4,7]; c5:bw=56,experts=[0,1,3,6,7]; c6:bw=13,experts=[3]; c7:bw=44,experts=[0,3,4,7]; c9:bw=53,experts=[0,1,3,5,6]; c1:bw=54,experts=[0,2,3,5,6]</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>7.3396,1.3094,2.7173,4.2367,8.0473,2.2542,9.3738,12.3112,3.0679,10.8535</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:25:56</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6089557731835937</v>
+      </c>
+      <c r="F51" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="G51" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H51" t="n">
+        <v>50</v>
+      </c>
+      <c r="I51" t="n">
+        <v>64.3866</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1:04.39</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>61.7877</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.4619</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3201.9104</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>53:21.91</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>8,4,7,6,2,1,3,0,9,5</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>8:32;4:10;7:34;6:68;2:63;1:64;3:39;0:29;9:27;5:31</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>8:[0,1,3];4:[3];7:[0,3,7];6:[0,1,3,4,5,7];2:[0,2,3,4,5,7];1:[0,1,2,3,6,7];3:[0,3,6];0:[0,3];9:[3,4];5:[0,3,7]</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>c8:bw=32,experts=[0,1,3]; c4:bw=10,experts=[3]; c7:bw=34,experts=[0,3,7]; c6:bw=68,experts=[0,1,3,4,5,7]; c2:bw=63,experts=[0,2,3,4,5,7]; c1:bw=64,experts=[0,1,2,3,6,7]; c3:bw=39,experts=[0,3,6]; c0:bw=29,experts=[0,3]; c9:bw=27,experts=[3,4]; c5:bw=31,experts=[0,3,7]</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2.7035,7.2487,12.4689,9.5564,8.0683,10.8984,1.3093,4.2386,3.0667,2.2290</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:27:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.6111802368853917</v>
+      </c>
+      <c r="F52" t="n">
+        <v>94.71035648432698</v>
+      </c>
+      <c r="G52" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" t="n">
+        <v>64.0829</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1:04.08</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>61.4519</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.4965</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3266.0172</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>54:26.02</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>5,0,1,2,8,6,9,3,4,7</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>5:47;0:53;1:21;2:20;8:46;6:52;9:18;3:55;4:11;7:27</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>5:[0,3,6,7];0:[0,2,3,6,7];1:[0,3];2:[1,6];8:[0,3,6,7];6:[2,3,4,5,7];9:[3];3:[0,1,2,3,6];4:[3];7:[3,7]</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>c5:bw=47,experts=[0,3,6,7]; c0:bw=53,experts=[0,2,3,6,7]; c1:bw=21,experts=[0,3]; c2:bw=20,experts=[1,6]; c8:bw=46,experts=[0,3,6,7]; c6:bw=52,experts=[2,3,4,5,7]; c9:bw=18,experts=[3]; c3:bw=55,experts=[0,1,2,3,6]; c4:bw=11,experts=[3]; c7:bw=27,experts=[3,7]</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2.2640,4.3012,10.7525,8.0075,2.7050,9.5521,3.0725,1.3254,7.1759,12.2957</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:28:05</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6149881157609233</v>
+      </c>
+      <c r="F53" t="n">
+        <v>94.92931776275353</v>
+      </c>
+      <c r="G53" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50</v>
+      </c>
+      <c r="I53" t="n">
+        <v>64.562</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1:04.56</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>61.8921</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.5366</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3330.6031</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>55:30.60</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0,8,5,7,1,4,9,6,2,3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>0:46;8:18;5:24;7:34;1:40;4:33;9:31;6:51;2:29;3:43</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0:[0,3,6,7];8:[3];5:[0,3];7:[3,5,7];1:[0,3,6,7];4:[0,3,7];9:[0,3,6];6:[1,3,4,5,7];2:[0,3];3:[0,2,3,6]</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>c0:bw=46,experts=[0,3,6,7]; c8:bw=18,experts=[3]; c5:bw=24,experts=[0,3]; c7:bw=34,experts=[3,5,7]; c1:bw=40,experts=[0,3,6,7]; c4:bw=33,experts=[0,3,7]; c9:bw=31,experts=[0,3,6]; c6:bw=51,experts=[1,3,4,5,7]; c2:bw=29,experts=[0,3]; c3:bw=43,experts=[0,2,3,6]</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4.2724,2.6835,2.3027,12.4444,10.9470,7.3250,3.0884,9.5626,7.9515,1.3147</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:29:09</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.6077529318475506</v>
+      </c>
+      <c r="F54" t="n">
+        <v>95.07145052243392</v>
+      </c>
+      <c r="G54" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H54" t="n">
+        <v>50</v>
+      </c>
+      <c r="I54" t="n">
+        <v>64.33029999999999</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1:04.33</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>61.7524</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.4515</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3394.9583</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>56:34.96</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>8,4,5,1,3,9,6,7,0,2</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>8:22;4:28;5:44;1:59;3:47;9:61;6:36;7:44;0:39;2:51</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8:[0,3];4:[0,3];5:[0,3,5,7];1:[0,2,3,6,7];3:[0,2,3,6];9:[0,1,3,4,6,7];6:[3,4,5];7:[0,3,4,7];0:[0,1,3];2:[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>c8:bw=22,experts=[0,3]; c4:bw=28,experts=[0,3]; c5:bw=44,experts=[0,3,5,7]; c1:bw=59,experts=[0,2,3,6,7]; c3:bw=47,experts=[0,2,3,6]; c9:bw=61,experts=[0,1,3,4,6,7]; c6:bw=36,experts=[3,4,5]; c7:bw=44,experts=[0,3,4,7]; c0:bw=39,experts=[0,1,3]; c2:bw=51,experts=[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2.7206,7.2761,2.2470,10.9082,1.3285,3.1052,9.4561,12.4212,4.2633,8.0261</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:14</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.6063155838445737</v>
+      </c>
+      <c r="F55" t="n">
+        <v>95.07145052243392</v>
+      </c>
+      <c r="G55" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H55" t="n">
+        <v>50</v>
+      </c>
+      <c r="I55" t="n">
+        <v>64.77330000000001</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1:04.77</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>62.1909</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.4546</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3459.7559</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>57:39.76</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2,1,8,7,3,0,6,5,9,4</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2:10;1:53;8:55;7:61;3:30;0:37;6:54;5:10;9:50;4:32</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2:[3];1:[0,2,3,6,7];8:[0,2,3,4,6];7:[0,1,2,3,4,7];3:[2,3,6];0:[0,3,4];6:[1,3,4,5,7];5:[3];9:[0,2,3,4,6];4:[0,3,4]</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>c2:bw=10,experts=[3]; c1:bw=53,experts=[0,2,3,6,7]; c8:bw=55,experts=[0,2,3,4,6]; c7:bw=61,experts=[0,1,2,3,4,7]; c3:bw=30,experts=[2,3,6]; c0:bw=37,experts=[0,3,4]; c6:bw=54,experts=[1,3,4,5,7]; c5:bw=10,experts=[3]; c9:bw=50,experts=[0,2,3,4,6]; c4:bw=32,experts=[0,3,4]</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>8.0109,11.0832,2.7231,12.6108,1.3142,4.2697,9.5840,2.2351,3.0944,7.2654</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:31:18</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.6047290278545768</v>
+      </c>
+      <c r="F56" t="n">
+        <v>94.47602950215119</v>
+      </c>
+      <c r="G56" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H56" t="n">
+        <v>50</v>
+      </c>
+      <c r="I56" t="n">
+        <v>64.2676</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1:04.27</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>61.6956</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2.4457</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3524.0495</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>58:44.05</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>7,2,4,3,8,5,1,6,0,9</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>7:54;2:41;4:14;3:52;8:14;5:53;1:60;6:42;0:27;9:62</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>7:[0,2,3,4,7];2:[0,3,4,7];4:[3];3:[0,3,4,6,7];8:[3];5:[0,3,4,6,7];1:[0,1,2,3,6,7];6:[0,2,3,7];0:[0,3];9:[0,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>c7:bw=54,experts=[0,2,3,4,7]; c2:bw=41,experts=[0,3,4,7]; c4:bw=14,experts=[3]; c3:bw=52,experts=[0,3,4,6,7]; c8:bw=14,experts=[3]; c5:bw=53,experts=[0,3,4,6,7]; c1:bw=60,experts=[0,1,2,3,6,7]; c6:bw=42,experts=[0,2,3,7]; c0:bw=27,experts=[0,3]; c9:bw=62,experts=[0,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>12.5584,8.0080,7.1797,1.3163,2.6629,2.2632,10.8566,9.5153,4.2409,3.0942</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:32:22</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.6076709065704387</v>
+      </c>
+      <c r="F57" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="G57" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H57" t="n">
+        <v>50</v>
+      </c>
+      <c r="I57" t="n">
+        <v>63.8705</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1:03.87</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>61.3008</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1336</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.4331</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3587.946</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>59:47.95</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>9,1,3,2,5,4,8,7,6,0</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>9:52;1:56;3:10;2:53;5:31;4:10;8:13;7:18;6:23;0:70</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>9:[0,1,3,4,6];1:[0,3,4,6,7];3:[3];2:[0,2,3,4,7];5:[0,2,3];4:[1];8:[3];7:[6];6:[3,6];0:[0,2,3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>c9:bw=52,experts=[0,1,3,4,6]; c1:bw=56,experts=[0,3,4,6,7]; c3:bw=10,experts=[3]; c2:bw=53,experts=[0,2,3,4,7]; c5:bw=31,experts=[0,2,3]; c4:bw=10,experts=[1]; c8:bw=13,experts=[3]; c7:bw=18,experts=[6]; c6:bw=23,experts=[3,6]; c0:bw=70,experts=[0,2,3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>3.0882,10.8414,1.3119,7.9828,2.2716,7.1864,2.6625,12.1457,9.4968,4.3135</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:33:27</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.6657528556186035</v>
+      </c>
+      <c r="F58" t="n">
+        <v>94.14182544560541</v>
+      </c>
+      <c r="G58" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H58" t="n">
+        <v>50</v>
+      </c>
+      <c r="I58" t="n">
+        <v>64.5797</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1:04.58</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>61.8789</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1353</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.5624</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3652.5516</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1:00:52.55</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>3,8,6,1,7,0,5,4,2,9</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>3:64;8:43;6:48;1:49;7:69;0:70;5:44;4:41;2:33;9:19</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>3:[0,1,2,3,5,6];8:[0,3,5,6];6:[2,3,5,7];1:[0,3,5,6];7:[0,2,3,4,6,7];0:[0,2,3,4,5,6,7];5:[0,1,3,7];4:[2,3,5,6];2:[2,3,7];9:[5]</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>c3:bw=64,experts=[0,1,2,3,5,6]; c8:bw=43,experts=[0,3,5,6]; c6:bw=48,experts=[2,3,5,7]; c1:bw=49,experts=[0,3,5,6]; c7:bw=69,experts=[0,2,3,4,6,7]; c0:bw=70,experts=[0,2,3,4,5,6,7]; c5:bw=44,experts=[0,1,3,7]; c4:bw=41,experts=[2,3,5,6]; c2:bw=33,experts=[2,3,7]; c9:bw=19,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>1.3425,2.7130,9.5142,10.8694,12.4712,4.3065,2.2737,7.3045,8.0289,3.0550</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:34:31</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.6210307491216918</v>
+      </c>
+      <c r="F59" t="n">
+        <v>95.06760909649662</v>
+      </c>
+      <c r="G59" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H59" t="n">
+        <v>50</v>
+      </c>
+      <c r="I59" t="n">
+        <v>64.08580000000001</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1:04.09</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>61.4535</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2.4949</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3716.6644</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1:01:56.66</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>7,2,9,6,5,1,8,4,3,0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>7:24;2:10;9:57;6:55;5:35;1:30;8:40;4:38;3:61;0:47</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>7:[3,7];2:[5];9:[0,1,2,3,6];6:[1,3,4,5,7];5:[0,3,7];1:[0,3,6];8:[0,1,3,6];4:[0,3,7];3:[0,1,2,3,4,6];0:[0,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>c7:bw=24,experts=[3,7]; c2:bw=10,experts=[5]; c9:bw=57,experts=[0,1,2,3,6]; c6:bw=55,experts=[1,3,4,5,7]; c5:bw=35,experts=[0,3,7]; c1:bw=30,experts=[0,3,6]; c8:bw=40,experts=[0,1,3,6]; c4:bw=38,experts=[0,3,7]; c3:bw=61,experts=[0,1,2,3,4,6]; c0:bw=47,experts=[0,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>12.3782,7.9200,3.0917,9.5436,2.2442,10.7450,2.6774,7.2762,1.3300,4.2472</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:35:35</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.6128692346118821</v>
+      </c>
+      <c r="F60" t="n">
+        <v>95.00998770743701</v>
+      </c>
+      <c r="G60" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H60" t="n">
+        <v>50</v>
+      </c>
+      <c r="I60" t="n">
+        <v>64.24290000000001</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1:04.24</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>61.6583</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2.4523</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3780.9341</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1:03:00.93</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2,8,9,6,1,4,7,5,0,3</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2:37;8:56;9:28;6:19;1:65;4:26;7:28;5:32;0:52;3:35</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2:[1,3,6];8:[0,2,3,6,7];9:[0,3];6:[3];1:[0,1,2,3,6,7];4:[0,3];7:[3,7];5:[0,3,7];0:[0,3,4,6,7];3:[0,3,6]</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>c2:bw=37,experts=[1,3,6]; c8:bw=56,experts=[0,2,3,6,7]; c9:bw=28,experts=[0,3]; c6:bw=19,experts=[3]; c1:bw=65,experts=[0,1,2,3,6,7]; c4:bw=26,experts=[0,3]; c7:bw=28,experts=[3,7]; c5:bw=32,experts=[0,3,7]; c0:bw=52,experts=[0,3,4,6,7]; c3:bw=35,experts=[0,3,6]</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>8.0393,2.7286,3.0864,9.4568,10.9006,7.2776,12.3291,2.2478,4.2787,1.3134</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:36:40</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.6053331466501684</v>
+      </c>
+      <c r="F61" t="n">
+        <v>95.04840196681008</v>
+      </c>
+      <c r="G61" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H61" t="n">
+        <v>50</v>
+      </c>
+      <c r="I61" t="n">
+        <v>64.4716</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1:04.47</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>61.803</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2.5255</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3845.4327</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1:04:05.43</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0,7,4,2,5,8,6,9,1,3</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>0:53;7:48;4:30;2:30;5:33;8:24;6:59;9:10;1:54;3:44</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0:[0,3,4,6,7];7:[3,4,5,7];4:[0,3,7];2:[2,3,7];5:[0,3,6];8:[0,3];6:[2,3,4,5,7];9:[3];1:[0,2,3,6,7];3:[1,2,3,6]</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>c0:bw=53,experts=[0,3,4,6,7]; c7:bw=48,experts=[3,4,5,7]; c4:bw=30,experts=[0,3,7]; c2:bw=30,experts=[2,3,7]; c5:bw=33,experts=[0,3,6]; c8:bw=24,experts=[0,3]; c6:bw=59,experts=[2,3,4,5,7]; c9:bw=10,experts=[3]; c1:bw=54,experts=[0,2,3,6,7]; c3:bw=44,experts=[1,2,3,6]</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>4.3073,12.4790,7.2902,8.0155,2.2429,2.6970,9.4957,3.0926,10.8443,1.3385</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:37:44</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.6045415872594362</v>
+      </c>
+      <c r="F62" t="n">
+        <v>94.82944068838353</v>
+      </c>
+      <c r="G62" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H62" t="n">
+        <v>50</v>
+      </c>
+      <c r="I62" t="n">
+        <v>64.4692</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1:04.47</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>61.8332</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.5067</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3909.929</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1:05:09.93</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>5,6,2,9,1,3,8,4,7,0</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>5:49;6:37;2:29;9:38;1:33;3:43;8:55;4:38;7:43;0:60</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>5:[0,3,5,6];6:[3,4,5];2:[2,3];9:[0,3,6];1:[0,3,6];3:[0,2,3,6];8:[0,2,3,6,7];4:[0,3,7];7:[0,3,4,7];0:[0,1,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>c5:bw=49,experts=[0,3,5,6]; c6:bw=37,experts=[3,4,5]; c2:bw=29,experts=[2,3]; c9:bw=38,experts=[0,3,6]; c1:bw=33,experts=[0,3,6]; c3:bw=43,experts=[0,2,3,6]; c8:bw=55,experts=[0,2,3,6,7]; c4:bw=38,experts=[0,3,7]; c7:bw=43,experts=[0,3,4,7]; c0:bw=60,experts=[0,1,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2.2799,9.5574,8.0201,3.1263,10.7720,1.3259,2.7002,7.2597,12.4470,4.3448</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:38:49</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.602896997055544</v>
+      </c>
+      <c r="F63" t="n">
+        <v>94.99078057775046</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H63" t="n">
+        <v>50</v>
+      </c>
+      <c r="I63" t="n">
+        <v>64.61060000000001</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1:04.61</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>61.962</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2.5172</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3974.5676</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1:06:14.57</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>8,6,9,4,5,0,3,2,1,7</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>8:13;6:62;9:16;4:60;5:67;0:28;3:53;2:42;1:75;7:44</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>8:[4];6:[1,2,3,4,5,7];9:[3];4:[0,2,3,4,6,7];5:[0,1,2,3,6,7];0:[0,3];3:[1,2,3,4,6];2:[2,3,4,7];1:[0,1,2,3,4,6,7];7:[1,3,4,7]</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>c8:bw=13,experts=[4]; c6:bw=62,experts=[1,2,3,4,5,7]; c9:bw=16,experts=[3]; c4:bw=60,experts=[0,2,3,4,6,7]; c5:bw=67,experts=[0,1,2,3,6,7]; c0:bw=28,experts=[0,3]; c3:bw=53,experts=[1,2,3,4,6]; c2:bw=42,experts=[2,3,4,7]; c1:bw=75,experts=[0,1,2,3,4,6,7]; c7:bw=44,experts=[1,3,4,7]</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2.6852,9.5978,3.0625,7.3627,2.2442,4.2534,1.3194,7.9820,10.9314,12.5233</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:39:53</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.6039941906810887</v>
+      </c>
+      <c r="F64" t="n">
+        <v>94.95236631837739</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="H64" t="n">
+        <v>50</v>
+      </c>
+      <c r="I64" t="n">
+        <v>64.1709</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1:04.17</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>61.604</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2.4372</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4038.7664</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1:07:18.77</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>5,9,6,3,8,1,7,0,2,4</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>5:10;9:21;6:34;3:52;8:32;1:50;7:68;0:41;2:28;4:52</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>5:[4];9:[3,7];6:[0,3,5];3:[1,2,3,6,7];8:[0,3,6];1:[0,2,3,6,7];7:[0,2,3,4,5,7];0:[0,3,6,7];2:[3,7];4:[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>c5:bw=10,experts=[4]; c9:bw=21,experts=[3,7]; c6:bw=34,experts=[0,3,5]; c3:bw=52,experts=[1,2,3,6,7]; c8:bw=32,experts=[0,3,6]; c1:bw=50,experts=[0,2,3,6,7]; c7:bw=68,experts=[0,2,3,4,5,7]; c0:bw=41,experts=[0,3,6,7]; c2:bw=28,experts=[3,7]; c4:bw=52,experts=[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2.2351,3.1024,9.4826,1.3186,2.6897,10.8101,12.4504,4.2859,7.9563,7.2729</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:40:58</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.6004068934606204</v>
+      </c>
+      <c r="F65" t="n">
+        <v>95.159803318992</v>
+      </c>
+      <c r="G65" t="n">
+        <v>95.159803318992</v>
+      </c>
+      <c r="H65" t="n">
+        <v>64</v>
+      </c>
+      <c r="I65" t="n">
+        <v>64.3515</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1:04.35</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>61.7148</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.1329</v>
+      </c>
+      <c r="M65" t="n">
+        <v>2.503</v>
+      </c>
+      <c r="N65" t="n">
+        <v>4103.1447</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1:08:23.14</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>6,4,5,3,7,0,8,9,2,1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>6:50;4:38;5:24;3:38;7:34;0:32;8:53;9:59;2:56;1:28</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>6:[2,3,4,5,6];4:[0,1,3];5:[0,3];3:[0,3,6];7:[0,3,7];0:[0,3,7];8:[0,2,3,6,7];9:[0,2,3,4,6];2:[0,2,3,4,7];1:[3,6]</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>c6:bw=50,experts=[2,3,4,5,6]; c4:bw=38,experts=[0,1,3]; c5:bw=24,experts=[0,3]; c3:bw=38,experts=[0,3,6]; c7:bw=34,experts=[0,3,7]; c0:bw=32,experts=[0,3,7]; c8:bw=53,experts=[0,2,3,6,7]; c9:bw=59,experts=[0,2,3,4,6]; c2:bw=56,experts=[0,2,3,4,7]; c1:bw=28,experts=[3,6]</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>9.5683,7.2676,2.2630,1.3218,12.4936,4.2611,2.7170,3.0954,8.0639,10.6631</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:42:02</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.600344154442052</v>
+      </c>
+      <c r="F66" t="n">
+        <v>95.17132759680393</v>
+      </c>
+      <c r="G66" t="n">
+        <v>95.17132759680393</v>
+      </c>
+      <c r="H66" t="n">
+        <v>65</v>
+      </c>
+      <c r="I66" t="n">
+        <v>64.018</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1:04.02</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>61.4678</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.1267</v>
+      </c>
+      <c r="M66" t="n">
+        <v>2.4227</v>
+      </c>
+      <c r="N66" t="n">
+        <v>4167.1906</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1:09:27.19</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>7,5,4,6,8,3,0,2,1,9</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>7:10;5:29;4:57;6:50;8:66;3:42;0:41;2:28;1:58;9:47</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>7:[6];5:[0,3];4:[0,2,3,5,7];6:[1,2,3,4,5];8:[0,2,3,5,6,7];3:[0,3,5,6];0:[0,2,3,5];2:[0,3];1:[0,3,5,6,7];9:[0,3,5,6]</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>c7:bw=10,experts=[6]; c5:bw=29,experts=[0,3]; c4:bw=57,experts=[0,2,3,5,7]; c6:bw=50,experts=[1,2,3,4,5]; c8:bw=66,experts=[0,2,3,5,6,7]; c3:bw=42,experts=[0,3,5,6]; c0:bw=41,experts=[0,2,3,5]; c2:bw=28,experts=[0,3]; c1:bw=58,experts=[0,3,5,6,7]; c9:bw=47,experts=[0,3,5,6]</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>12.2225,2.2575,7.2876,9.5647,2.7142,1.3178,4.3368,7.9667,10.7262,3.0739</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:43:06</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.6094357133553669</v>
+      </c>
+      <c r="F67" t="n">
+        <v>95.14443761524278</v>
+      </c>
+      <c r="G67" t="n">
+        <v>95.17132759680393</v>
+      </c>
+      <c r="H67" t="n">
+        <v>65</v>
+      </c>
+      <c r="I67" t="n">
+        <v>64.38460000000001</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1:04.38</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>61.7281</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2.5164</v>
+      </c>
+      <c r="N67" t="n">
+        <v>4231.6026</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1:10:31.60</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2,5,1,8,9,6,4,0,3,7</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2:41;5:17;1:54;8:24;9:31;6:30;4:41;0:38;3:66;7:50</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2:[3,4,5,7];5:[3];1:[0,2,3,6,7];8:[1,3];9:[0,1,3];6:[3,5,7];4:[0,2,3,7];0:[0,3,6];3:[0,1,2,3,4,6];7:[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>c2:bw=41,experts=[3,4,5,7]; c5:bw=17,experts=[3]; c1:bw=54,experts=[0,2,3,6,7]; c8:bw=24,experts=[1,3]; c9:bw=31,experts=[0,1,3]; c6:bw=30,experts=[3,5,7]; c4:bw=41,experts=[0,2,3,7]; c0:bw=38,experts=[0,3,6]; c3:bw=66,experts=[0,1,2,3,4,6]; c7:bw=50,experts=[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>8.1050,2.2600,10.8811,2.6776,3.0940,9.4632,7.2985,4.2291,1.3112,12.4085</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:44:11</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.5985255580744554</v>
+      </c>
+      <c r="F68" t="n">
+        <v>95.15596189305471</v>
+      </c>
+      <c r="G68" t="n">
+        <v>95.17132759680393</v>
+      </c>
+      <c r="H68" t="n">
+        <v>65</v>
+      </c>
+      <c r="I68" t="n">
+        <v>64.5688</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1:04.57</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>61.9225</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2.5127</v>
+      </c>
+      <c r="N68" t="n">
+        <v>4296.1997</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1:11:36.20</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>4,5,1,3,6,0,2,9,7,8</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4:51;5:48;1:36;3:25;6:53;0:32;2:43;9:60;7:59;8:10</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>4:[0,2,3,6,7];5:[0,2,3,6];1:[0,3,6];3:[3,6];6:[2,3,4,5,7];0:[0,3,7];2:[1,3,6,7];9:[0,1,2,3,4,6];7:[0,2,3,4,7];8:[3]</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>c4:bw=51,experts=[0,2,3,6,7]; c5:bw=48,experts=[0,2,3,6]; c1:bw=36,experts=[0,3,6]; c3:bw=25,experts=[3,6]; c6:bw=53,experts=[2,3,4,5,7]; c0:bw=32,experts=[0,3,7]; c2:bw=43,experts=[1,3,6,7]; c9:bw=60,experts=[0,1,2,3,4,6]; c7:bw=59,experts=[0,2,3,4,7]; c8:bw=10,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>7.3847,2.2883,10.8441,1.3037,9.6023,4.2408,7.9607,3.1006,12.5298,2.6673</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:45:15</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.597145823676833</v>
+      </c>
+      <c r="F69" t="n">
+        <v>95.32882606023355</v>
+      </c>
+      <c r="G69" t="n">
+        <v>95.32882606023355</v>
+      </c>
+      <c r="H69" t="n">
+        <v>68</v>
+      </c>
+      <c r="I69" t="n">
+        <v>64.37050000000001</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1:04.37</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>61.7297</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2.4985</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4360.5988</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1:12:40.60</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1,8,2,0,3,4,5,9,7,6</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1:42;8:31;2:58;0:30;3:26;4:49;5:45;9:15;7:28;6:32</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1:[0,3,6,7];8:[0,3,6];2:[0,2,3,4,7];0:[0,3,7];3:[3,6];4:[0,2,3,7];5:[0,2,3,6];9:[3];7:[3,7];6:[3,5,7]</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>c1:bw=42,experts=[0,3,6,7]; c8:bw=31,experts=[0,3,6]; c2:bw=58,experts=[0,2,3,4,7]; c0:bw=30,experts=[0,3,7]; c3:bw=26,experts=[3,6]; c4:bw=49,experts=[0,2,3,7]; c5:bw=45,experts=[0,2,3,6]; c9:bw=15,experts=[3]; c7:bw=28,experts=[3,7]; c6:bw=32,experts=[3,5,7]</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>10.8484,2.7106,8.0931,4.2575,1.3067,7.2785,2.2397,3.0762,12.4013,9.5178</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:46:19</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.5950379776242856</v>
+      </c>
+      <c r="F70" t="n">
+        <v>95.34419176398279</v>
+      </c>
+      <c r="G70" t="n">
+        <v>95.34419176398279</v>
+      </c>
+      <c r="H70" t="n">
+        <v>69</v>
+      </c>
+      <c r="I70" t="n">
+        <v>64.4068</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1:04.41</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>61.8061</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4425.0341</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1:13:45.03</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>3,7,1,4,9,5,0,2,8,6</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>3:41;7:58;1:31;4:41;9:35;5:39;0:52;2:66;8:42;6:26</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>3:[0,1,3,6];7:[0,2,3,4,7];1:[0,3,6];4:[0,2,3,7];9:[0,3,6];5:[0,3,5];0:[0,1,3,4,7];2:[0,2,3,4,5,7];8:[0,3,6,7];6:[3,7]</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>c3:bw=41,experts=[0,1,3,6]; c7:bw=58,experts=[0,2,3,4,7]; c1:bw=31,experts=[0,3,6]; c4:bw=41,experts=[0,2,3,7]; c9:bw=35,experts=[0,3,6]; c5:bw=39,experts=[0,3,5]; c0:bw=52,experts=[0,1,3,4,7]; c2:bw=66,experts=[0,2,3,4,5,7]; c8:bw=42,experts=[0,3,6,7]; c6:bw=26,experts=[3,7]</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>1.3153,12.5275,10.7820,7.2915,3.0970,2.2594,4.3082,8.0970,2.6811,9.4471</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:47:23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.5966950538676647</v>
+      </c>
+      <c r="F71" t="n">
+        <v>94.92163491087892</v>
+      </c>
+      <c r="G71" t="n">
+        <v>95.34419176398279</v>
+      </c>
+      <c r="H71" t="n">
+        <v>69</v>
+      </c>
+      <c r="I71" t="n">
+        <v>63.9961</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1:04.00</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>61.4162</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N71" t="n">
+        <v>4489.0603</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1:14:49.06</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1,9,7,3,0,6,2,4,5,8</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1:24;9:10;7:28;3:32;0:30;6:26;2:55;4:58;5:23;8:48</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1:[1,4];9:[3];7:[1,3];3:[0,3,6];0:[0,3,7];6:[3,7];2:[0,2,3,4,7];4:[0,2,3,4,7];5:[1,7];8:[0,3,4,6]</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>c1:bw=24,experts=[1,4]; c9:bw=10,experts=[3]; c7:bw=28,experts=[1,3]; c3:bw=32,experts=[0,3,6]; c0:bw=30,experts=[0,3,7]; c6:bw=26,experts=[3,7]; c2:bw=55,experts=[0,2,3,4,7]; c4:bw=58,experts=[0,2,3,4,7]; c5:bw=23,experts=[1,7]; c8:bw=48,experts=[0,3,4,6]</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>10.7205,3.0709,12.3960,1.3132,4.2691,9.4626,8.0155,7.2963,2.2153,2.6567</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:48:28</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6062611054834368</v>
+      </c>
+      <c r="F72" t="n">
+        <v>95.11370620774431</v>
+      </c>
+      <c r="G72" t="n">
+        <v>95.34419176398279</v>
+      </c>
+      <c r="H72" t="n">
+        <v>69</v>
+      </c>
+      <c r="I72" t="n">
+        <v>64.5941</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1:04.59</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>61.9121</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="M72" t="n">
+        <v>2.5508</v>
+      </c>
+      <c r="N72" t="n">
+        <v>4553.6835</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1:15:53.68</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>4,0,1,9,7,5,3,6,8,2</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>4:42;0:16;1:52;9:40;7:20;5:33;3:62;6:50;8:39;2:61</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>4:[0,2,3,7];0:[3];1:[0,2,3,6,7];9:[0,3,6,7];7:[3,5];5:[0,3,4];3:[1,2,3,4,6,7];6:[0,2,3,4,7];8:[0,3,6];2:[0,2,3,4,5,7]</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>c4:bw=42,experts=[0,2,3,7]; c0:bw=16,experts=[3]; c1:bw=52,experts=[0,2,3,6,7]; c9:bw=40,experts=[0,3,6,7]; c7:bw=20,experts=[3,5]; c5:bw=33,experts=[0,3,4]; c3:bw=62,experts=[1,2,3,4,6,7]; c6:bw=50,experts=[0,2,3,4,7]; c8:bw=39,experts=[0,3,6]; c2:bw=61,experts=[0,2,3,4,5,7]</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>7.3104,4.2655,10.9541,3.1018,12.4450,2.2471,1.3148,9.5324,2.6760,8.0649</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:49:32</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.6007557114861944</v>
+      </c>
+      <c r="F73" t="n">
+        <v>95.16748617086662</v>
+      </c>
+      <c r="G73" t="n">
+        <v>95.34419176398279</v>
+      </c>
+      <c r="H73" t="n">
+        <v>69</v>
+      </c>
+      <c r="I73" t="n">
+        <v>63.8722</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1:03.87</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>61.2956</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="M73" t="n">
+        <v>2.4388</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4617.5853</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1:16:57.59</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>8,1,5,7,6,0,3,2,9,4</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>8:30;1:39;5:43;7:48;6:19;0:52;3:23;2:23;9:38;4:39</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>8:[0,3,6];1:[0,3,6];5:[0,2,3,6];7:[0,3,4,7];6:[6];0:[0,2,3,6,7];3:[3,6];2:[2,3];9:[0,3,6];4:[0,1,3]</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>c8:bw=30,experts=[0,3,6]; c1:bw=39,experts=[0,3,6]; c5:bw=43,experts=[0,2,3,6]; c7:bw=48,experts=[0,3,4,7]; c6:bw=19,experts=[6]; c0:bw=52,experts=[0,2,3,6,7]; c3:bw=23,experts=[3,6]; c2:bw=23,experts=[2,3]; c9:bw=38,experts=[0,3,6]; c4:bw=39,experts=[0,1,3]</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2.6645,10.8138,2.2670,12.4801,9.2515,4.3136,1.3010,7.9474,3.0785,7.1783</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:50:36</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.6148993040582279</v>
+      </c>
+      <c r="F74" t="n">
+        <v>94.88322065150584</v>
+      </c>
+      <c r="G74" t="n">
+        <v>95.34419176398279</v>
+      </c>
+      <c r="H74" t="n">
+        <v>69</v>
+      </c>
+      <c r="I74" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1:04.08</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>61.4293</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2.522</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4681.6948</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1:18:01.69</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2,8,3,1,5,9,0,7,6,4</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2:47;8:11;3:40;1:66;5:17;9:52;0:28;7:37;6:20;4:41</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2:[0,2,3,7];8:[2];3:[2,3,5,6];1:[0,2,3,5,6,7];5:[3];9:[0,2,3,5,6];0:[3,5];7:[3,6,7];6:[1,3];4:[0,2,3,5]</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>c2:bw=47,experts=[0,2,3,7]; c8:bw=11,experts=[2]; c3:bw=40,experts=[2,3,5,6]; c1:bw=66,experts=[0,2,3,5,6,7]; c5:bw=17,experts=[3]; c9:bw=52,experts=[0,2,3,5,6]; c0:bw=28,experts=[3,5]; c7:bw=37,experts=[3,6,7]; c6:bw=20,experts=[1,3]; c4:bw=41,experts=[0,2,3,5]</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>8.0657,2.6324,1.3161,10.7560,2.2309,3.1038,4.2372,12.3974,9.3933,7.2964</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:51:40</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.6067902288322524</v>
+      </c>
+      <c r="F75" t="n">
+        <v>95.3480331899201</v>
+      </c>
+      <c r="G75" t="n">
+        <v>95.3480331899201</v>
+      </c>
+      <c r="H75" t="n">
+        <v>74</v>
+      </c>
+      <c r="I75" t="n">
+        <v>63.9263</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1:03.93</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>61.328</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1377</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.4575</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4745.6516</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1:19:05.65</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>3,0,1,5,7,8,6,2,4,9</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>3:10;0:40;1:28;5:50;7:65;8:28;6:10;2:10;4:47;9:32</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>3:[3];0:[0,3,4,7];1:[0,3];5:[0,2,3,6,7];7:[0,2,3,4,5,7];8:[1,5];6:[3];2:[3];4:[0,2,3,7];9:[0,3,6]</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[3]; c0:bw=40,experts=[0,3,4,7]; c1:bw=28,experts=[0,3]; c5:bw=50,experts=[0,2,3,6,7]; c7:bw=65,experts=[0,2,3,4,5,7]; c8:bw=28,experts=[1,5]; c6:bw=10,experts=[3]; c2:bw=10,experts=[3]; c4:bw=47,experts=[0,2,3,7]; c9:bw=32,experts=[0,3,6]</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>1.3076,4.2728,10.7236,2.2458,12.4539,2.6207,9.3939,7.9510,7.2632,3.0956</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:52:44</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.5954561471868626</v>
+      </c>
+      <c r="F76" t="n">
+        <v>95.2980946527351</v>
+      </c>
+      <c r="G76" t="n">
+        <v>95.3480331899201</v>
+      </c>
+      <c r="H76" t="n">
+        <v>74</v>
+      </c>
+      <c r="I76" t="n">
+        <v>64.3753</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1:04.38</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>61.7896</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2.4459</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4810.0579</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1:20:10.06</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2,9,1,3,7,6,5,4,0,8</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2:40;9:61;1:54;3:20;7:28;6:56;5:31;4:56;0:60;8:53</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2:[1,2,3,6];9:[0,1,2,3,4,6];1:[0,2,3,6,7];3:[3,6];7:[0,3];6:[2,3,4,5,7];5:[0,3,6];4:[0,2,3,6,7];0:[0,2,3,4,6,7];8:[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>c2:bw=40,experts=[1,2,3,6]; c9:bw=61,experts=[0,1,2,3,4,6]; c1:bw=54,experts=[0,2,3,6,7]; c3:bw=20,experts=[3,6]; c7:bw=28,experts=[0,3]; c6:bw=56,experts=[2,3,4,5,7]; c5:bw=31,experts=[0,3,6]; c4:bw=56,experts=[0,2,3,6,7]; c0:bw=60,experts=[0,2,3,4,6,7]; c8:bw=53,experts=[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>8.0699,3.1299,10.8333,1.3091,12.3276,9.4961,2.2553,7.3782,4.3130,2.6771</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:53:49</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.5915966516444855</v>
+      </c>
+      <c r="F77" t="n">
+        <v>95.31346035648433</v>
+      </c>
+      <c r="G77" t="n">
+        <v>95.3480331899201</v>
+      </c>
+      <c r="H77" t="n">
+        <v>74</v>
+      </c>
+      <c r="I77" t="n">
+        <v>64.3141</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1:04.31</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>61.6731</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2.5089</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4874.4019</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1:21:14.40</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>8,5,0,3,2,6,7,4,9,1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>8:29;5:37;0:31;3:15;2:25;6:23;7:66;4:60;9:57;1:53</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>8:[0,3];5:[0,3,7];0:[0,3,7];3:[3];2:[0,3];6:[2,3];7:[0,2,3,4,5,7];4:[0,1,2,3,6,7];9:[0,1,2,3,6];1:[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>c8:bw=29,experts=[0,3]; c5:bw=37,experts=[0,3,7]; c0:bw=31,experts=[0,3,7]; c3:bw=15,experts=[3]; c2:bw=25,experts=[0,3]; c6:bw=23,experts=[2,3]; c7:bw=66,experts=[0,2,3,4,5,7]; c4:bw=60,experts=[0,1,2,3,6,7]; c9:bw=57,experts=[0,1,2,3,6]; c1:bw=53,experts=[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>2.6586,2.2372,4.2520,1.2858,7.9607,9.4846,12.4972,7.3242,3.1335,10.8393</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:54:53</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.5919079323984158</v>
+      </c>
+      <c r="F78" t="n">
+        <v>95.32882606023355</v>
+      </c>
+      <c r="G78" t="n">
+        <v>95.3480331899201</v>
+      </c>
+      <c r="H78" t="n">
+        <v>74</v>
+      </c>
+      <c r="I78" t="n">
+        <v>64.1439</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1:04.14</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>61.5219</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.1413</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2.4763</v>
+      </c>
+      <c r="N78" t="n">
+        <v>4938.5776</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1:22:18.58</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>9,2,1,8,4,7,6,0,3,5</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>9:29;2:34;1:62;8:10;4:10;7:10;6:57;0:63;3:40;5:59</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>9:[0,3];2:[0,3,7];1:[0,1,2,3,6,7];8:[3];4:[3];7:[3];6:[2,3,4,5,7];0:[0,1,2,3,6,7];3:[0,2,3,6];5:[0,2,3,5,7]</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>c9:bw=29,experts=[0,3]; c2:bw=34,experts=[0,3,7]; c1:bw=62,experts=[0,1,2,3,6,7]; c8:bw=10,experts=[3]; c4:bw=10,experts=[3]; c7:bw=10,experts=[3]; c6:bw=57,experts=[2,3,4,5,7]; c0:bw=63,experts=[0,1,2,3,6,7]; c3:bw=40,experts=[0,2,3,6]; c5:bw=59,experts=[0,2,3,5,7]</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>3.1096,7.9895,10.8193,2.6732,7.2641,12.3314,9.4618,4.2893,1.3094,2.2742</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:55:57</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.5905083706369287</v>
+      </c>
+      <c r="F79" t="n">
+        <v>94.99846342962508</v>
+      </c>
+      <c r="G79" t="n">
+        <v>95.3480331899201</v>
+      </c>
+      <c r="H79" t="n">
+        <v>74</v>
+      </c>
+      <c r="I79" t="n">
+        <v>64.2724</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1:04.27</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>61.6891</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.1235</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2.459</v>
+      </c>
+      <c r="N79" t="n">
+        <v>5002.8809</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1:23:22.88</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>0,4,3,7,8,1,9,6,5,2</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>0:26;4:23;3:38;7:36;8:54;1:41;9:31;6:57;5:63;2:34</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>0:[3,7];4:[3,4];3:[0,3,6];7:[1,3,7];8:[0,3,4,6,7];1:[0,3,4,6];9:[0,3,6];6:[2,3,4,5,7];5:[0,1,2,3,6,7];2:[0,2,3]</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>c0:bw=26,experts=[3,7]; c4:bw=23,experts=[3,4]; c3:bw=38,experts=[0,3,6]; c7:bw=36,experts=[1,3,7]; c8:bw=54,experts=[0,3,4,6,7]; c1:bw=41,experts=[0,3,4,6]; c9:bw=31,experts=[0,3,6]; c6:bw=57,experts=[2,3,4,5,7]; c5:bw=63,experts=[0,1,2,3,6,7]; c2:bw=34,experts=[0,2,3]</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>4.2866,7.3082,1.3188,12.4821,2.7027,10.7998,3.0709,9.5128,2.2560,7.9513</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:57:01</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.5933887794109578</v>
+      </c>
+      <c r="F80" t="n">
+        <v>95.22894898586355</v>
+      </c>
+      <c r="G80" t="n">
+        <v>95.3480331899201</v>
+      </c>
+      <c r="H80" t="n">
+        <v>74</v>
+      </c>
+      <c r="I80" t="n">
+        <v>64.0625</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1:04.06</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>61.4931</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.1284</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2.4403</v>
+      </c>
+      <c r="N80" t="n">
+        <v>5066.9746</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1:24:26.97</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>6,9,0,4,7,8,5,3,1,2</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>6:21;9:10;0:36;4:80;7:46;8:44;5:53;3:26;1:37;2:33</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>6:[0,3];9:[7];0:[0,3,7];4:[0,1,2,3,4,5,6,7];7:[0,3,4,7];8:[0,3,6,7];5:[0,3,4,6,7];3:[1,4];1:[0,3,6];2:[3,4,5]</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>c6:bw=21,experts=[0,3]; c9:bw=10,experts=[7]; c0:bw=36,experts=[0,3,7]; c4:bw=80,experts=[0,1,2,3,4,5,6,7]; c7:bw=46,experts=[0,3,4,7]; c8:bw=44,experts=[0,3,6,7]; c5:bw=53,experts=[0,3,4,6,7]; c3:bw=26,experts=[1,4]; c1:bw=37,experts=[0,3,6]; c2:bw=33,experts=[3,4,5]</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>9.5289,3.0660,4.2656,7.3154,12.4535,2.6632,2.2536,1.2806,10.6997,7.9665</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:58:06</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.5926595177888814</v>
+      </c>
+      <c r="F81" t="n">
+        <v>95.17901044867855</v>
+      </c>
+      <c r="G81" t="n">
+        <v>95.3480331899201</v>
+      </c>
+      <c r="H81" t="n">
+        <v>74</v>
+      </c>
+      <c r="I81" t="n">
+        <v>64.3809</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1:04.38</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>61.7925</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2.4448</v>
+      </c>
+      <c r="N81" t="n">
+        <v>5131.388</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1:25:31.39</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>5,9,7,1,3,4,2,0,6,8</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>5:65;9:53;7:48;1:31;3:31;4:57;2:44;0:47;6:39;8:51</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>5:[0,2,3,4,6,7];9:[0,1,3,4,6];7:[0,3,4,7];1:[0,3,6];3:[0,3,7];4:[0,2,3,6,7];2:[2,3,4,7];0:[0,3,6,7];6:[2,3,6];8:[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>c5:bw=65,experts=[0,2,3,4,6,7]; c9:bw=53,experts=[0,1,3,4,6]; c7:bw=48,experts=[0,3,4,7]; c1:bw=31,experts=[0,3,6]; c3:bw=31,experts=[0,3,7]; c4:bw=57,experts=[0,2,3,6,7]; c2:bw=44,experts=[2,3,4,7]; c0:bw=47,experts=[0,3,6,7]; c6:bw=39,experts=[2,3,6]; c8:bw=51,experts=[0,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>2.2852,3.1444,12.5353,10.7792,1.3087,7.3232,7.9971,4.2314,9.4819,2.7062</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:59:10</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.5882658463486445</v>
+      </c>
+      <c r="F82" t="n">
+        <v>95.45943454210203</v>
+      </c>
+      <c r="G82" t="n">
+        <v>95.45943454210203</v>
+      </c>
+      <c r="H82" t="n">
+        <v>81</v>
+      </c>
+      <c r="I82" t="n">
+        <v>64.4832</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1:04.48</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>61.8485</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2.488</v>
+      </c>
+      <c r="N82" t="n">
+        <v>5195.9036</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1:26:35.90</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>6,2,3,1,4,5,9,7,8,0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>6:51;2:45;3:67;1:49;4:42;5:30;9:26;7:58;8:48;0:50</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>6:[1,2,3,5,7];2:[0,2,3,7];3:[1,2,3,4,5,6];1:[0,3,5,6];4:[0,2,3,7];5:[0,3,6];9:[3,5];7:[0,3,4,6,7];8:[0,2,3,6];0:[0,3,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>c6:bw=51,experts=[1,2,3,5,7]; c2:bw=45,experts=[0,2,3,7]; c3:bw=67,experts=[1,2,3,4,5,6]; c1:bw=49,experts=[0,3,5,6]; c4:bw=42,experts=[0,2,3,7]; c5:bw=30,experts=[0,3,6]; c9:bw=26,experts=[3,5]; c7:bw=58,experts=[0,3,4,6,7]; c8:bw=48,experts=[0,2,3,6]; c0:bw=50,experts=[0,3,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>9.6179,8.0846,1.3153,10.7716,7.2401,2.2684,3.0693,12.5342,2.6664,4.2807</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:00:14</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.5877905883549249</v>
+      </c>
+      <c r="F83" t="n">
+        <v>95.35571604179471</v>
+      </c>
+      <c r="G83" t="n">
+        <v>95.45943454210203</v>
+      </c>
+      <c r="H83" t="n">
+        <v>81</v>
+      </c>
+      <c r="I83" t="n">
+        <v>64.1206</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1:04.12</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>61.4909</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.1373</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2.4893</v>
+      </c>
+      <c r="N83" t="n">
+        <v>5260.0568</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1:27:40.06</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1,0,6,8,7,3,2,9,5,4</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1:64;0:30;6:36;8:58;7:40;3:39;2:30;9:56;5:40;4:30</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1:[0,1,2,3,6,7];0:[0,3,7];6:[2,3,7];8:[0,1,3,5,7];7:[0,3,4,7];3:[0,3,6];2:[0,3,7];9:[0,2,3,4,6];5:[0,3,6,7];4:[0,3,7]</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>c1:bw=64,experts=[0,1,2,3,6,7]; c0:bw=30,experts=[0,3,7]; c6:bw=36,experts=[2,3,7]; c8:bw=58,experts=[0,1,3,5,7]; c7:bw=40,experts=[0,3,4,7]; c3:bw=39,experts=[0,3,6]; c2:bw=30,experts=[0,3,7]; c9:bw=56,experts=[0,2,3,4,6]; c5:bw=40,experts=[0,3,6,7]; c4:bw=30,experts=[0,3,7]</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>10.9228,4.2390,9.4933,2.6462,12.4062,1.3128,7.9712,3.0956,2.2448,7.1590</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:01:19</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.5880278364761314</v>
+      </c>
+      <c r="F84" t="n">
+        <v>95.37108174554395</v>
+      </c>
+      <c r="G84" t="n">
+        <v>95.45943454210203</v>
+      </c>
+      <c r="H84" t="n">
+        <v>81</v>
+      </c>
+      <c r="I84" t="n">
+        <v>64.273</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1:04.27</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>61.6346</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.1413</v>
+      </c>
+      <c r="M84" t="n">
+        <v>2.4925</v>
+      </c>
+      <c r="N84" t="n">
+        <v>5324.3622</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1:28:44.36</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>9,4,2,7,5,0,6,1,8,3</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>9:51;4:10;2:41;7:37;5:10;0:10;6:53;1:63;8:39;3:42</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>9:[0,2,3,6,7];4:[3];2:[1,2,3,6];7:[0,3,7];5:[3];0:[4];6:[2,3,4,5,7];1:[0,2,3,4,6,7];8:[0,3,6];3:[0,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>c9:bw=51,experts=[0,2,3,6,7]; c4:bw=10,experts=[3]; c2:bw=41,experts=[1,2,3,6]; c7:bw=37,experts=[0,3,7]; c5:bw=10,experts=[3]; c0:bw=10,experts=[4]; c6:bw=53,experts=[2,3,4,5,7]; c1:bw=63,experts=[0,2,3,4,6,7]; c8:bw=39,experts=[0,3,6]; c3:bw=42,experts=[0,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>3.1123,7.1814,8.0349,12.5224,2.2454,4.2047,9.5847,10.7797,2.6568,1.3124</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:02:23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.5888833086374428</v>
+      </c>
+      <c r="F85" t="n">
+        <v>95.35955746773202</v>
+      </c>
+      <c r="G85" t="n">
+        <v>95.45943454210203</v>
+      </c>
+      <c r="H85" t="n">
+        <v>81</v>
+      </c>
+      <c r="I85" t="n">
+        <v>64.02970000000001</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1:04.03</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>61.4013</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="M85" t="n">
+        <v>2.4892</v>
+      </c>
+      <c r="N85" t="n">
+        <v>5388.425</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1:29:48.42</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>8,3,1,6,9,2,7,5,4,0</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>8:67;3:32;1:58;6:10;9:20;2:36;7:47;5:20;4:27;0:10</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>8:[0,1,2,3,6,7];3:[0,3,6];1:[0,2,3,6,7];6:[3];9:[0,3];2:[2,3,7];7:[2,3,5,7];5:[0,3];4:[0,3];0:[3]</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>c8:bw=67,experts=[0,1,2,3,6,7]; c3:bw=32,experts=[0,3,6]; c1:bw=58,experts=[0,2,3,6,7]; c6:bw=10,experts=[3]; c9:bw=20,experts=[0,3]; c2:bw=36,experts=[2,3,7]; c7:bw=47,experts=[2,3,5,7]; c5:bw=20,experts=[0,3]; c4:bw=27,experts=[0,3]; c0:bw=10,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>2.6658,1.3142,10.7689,9.4493,3.0868,8.0161,12.4427,2.2660,7.1618,4.2295</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:03:27</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.5896122748406666</v>
+      </c>
+      <c r="F86" t="n">
+        <v>94.89090350338046</v>
+      </c>
+      <c r="G86" t="n">
+        <v>95.45943454210203</v>
+      </c>
+      <c r="H86" t="n">
+        <v>81</v>
+      </c>
+      <c r="I86" t="n">
+        <v>64.22580000000001</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1:04.23</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>61.5863</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2.5008</v>
+      </c>
+      <c r="N86" t="n">
+        <v>5452.6838</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1:30:52.68</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>0,2,8,6,1,4,9,3,5,7</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>0:38;2:45;8:70;6:42;1:57;4:42;9:58;3:51;5:12;7:11</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>0:[1,2,3];2:[2,3,4,7];8:[0,1,2,3,4,6,7];6:[2,3,5,7];1:[0,2,3,6,7];4:[0,2,3,7];9:[0,1,3,4,6];3:[1,2,3,4,6];5:[5];7:[3]</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>c0:bw=38,experts=[1,2,3]; c2:bw=45,experts=[2,3,4,7]; c8:bw=70,experts=[0,1,2,3,4,6,7]; c6:bw=42,experts=[2,3,5,7]; c1:bw=57,experts=[0,2,3,6,7]; c4:bw=42,experts=[0,2,3,7]; c9:bw=58,experts=[0,1,3,4,6]; c3:bw=51,experts=[1,2,3,4,6]; c5:bw=12,experts=[5]; c7:bw=11,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>4.2729,8.0451,2.7000,9.5430,10.8203,7.2457,3.1131,1.3227,2.2080,12.3155</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:04:31</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.5887912942052106</v>
+      </c>
+      <c r="F87" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="G87" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H87" t="n">
+        <v>86</v>
+      </c>
+      <c r="I87" t="n">
+        <v>64.2569</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>1:04.26</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>61.6676</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="M87" t="n">
+        <v>2.4652</v>
+      </c>
+      <c r="N87" t="n">
+        <v>5516.9734</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1:31:56.97</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>5,8,2,6,0,4,7,3,1,9</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>5:47;8:28;2:24;6:55;0:30;4:18;7:44;3:28;1:72;9:43</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>5:[0,1,2,3];8:[0,3];2:[2,3];6:[1,2,3,4,7];0:[0,3,7];4:[3];7:[0,1,3,7];3:[3,6];1:[0,1,2,3,4,6,7];9:[0,2,3,6]</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>c5:bw=47,experts=[0,1,2,3]; c8:bw=28,experts=[0,3]; c2:bw=24,experts=[2,3]; c6:bw=55,experts=[1,2,3,4,7]; c0:bw=30,experts=[0,3,7]; c4:bw=18,experts=[3]; c7:bw=44,experts=[0,1,3,7]; c3:bw=28,experts=[3,6]; c1:bw=72,experts=[0,1,2,3,4,6,7]; c9:bw=43,experts=[0,2,3,6]</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>2.2756,2.6665,8.0174,9.5718,4.2494,7.1744,12.4950,1.2985,10.8214,3.0977</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:05:36</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.5894153078722713</v>
+      </c>
+      <c r="F88" t="n">
+        <v>95.3019360786724</v>
+      </c>
+      <c r="G88" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H88" t="n">
+        <v>86</v>
+      </c>
+      <c r="I88" t="n">
+        <v>64.2051</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1:04.21</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>61.6208</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2.4457</v>
+      </c>
+      <c r="N88" t="n">
+        <v>5581.2118</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1:33:01.21</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1,2,7,5,6,3,4,9,8,0</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1:29;2:67;7:22;5:10;6:60;3:68;4:34;9:37;8:46;0:35</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1:[0,3];2:[0,2,3,4,5,7];7:[3,7];5:[3];6:[0,2,3,4,5,7];3:[0,1,2,3,6,7];4:[1,4,5];9:[0,2,3];8:[0,2,3,6];0:[0,3,7]</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>c1:bw=29,experts=[0,3]; c2:bw=67,experts=[0,2,3,4,5,7]; c7:bw=22,experts=[3,7]; c5:bw=10,experts=[3]; c6:bw=60,experts=[0,2,3,4,5,7]; c3:bw=68,experts=[0,1,2,3,6,7]; c4:bw=34,experts=[1,4,5]; c9:bw=37,experts=[0,2,3]; c8:bw=46,experts=[0,2,3,6]; c0:bw=35,experts=[0,3,7]</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>10.7465,8.1335,12.4571,2.2244,9.5632,1.3213,7.1902,3.0798,2.6467,4.2580</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:06:40</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.5893495042887202</v>
+      </c>
+      <c r="F89" t="n">
+        <v>95.47095881991395</v>
+      </c>
+      <c r="G89" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H89" t="n">
+        <v>86</v>
+      </c>
+      <c r="I89" t="n">
+        <v>64.0706</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1:04.07</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>61.4657</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2.4716</v>
+      </c>
+      <c r="N89" t="n">
+        <v>5645.3157</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1:34:05.32</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>8,6,3,7,0,4,9,1,5,2</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>8:43;6:27;3:33;7:41;0:62;4:38;9:31;1:28;5:30;2:46</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>8:[0,2,3,6];6:[3,6];3:[2,3,6];7:[0,2,3,7];0:[0,2,3,4,6,7];4:[0,3,6];9:[0,3,6];1:[0,3];5:[0,3,4];2:[0,2,3,7]</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>c8:bw=43,experts=[0,2,3,6]; c6:bw=27,experts=[3,6]; c3:bw=33,experts=[2,3,6]; c7:bw=41,experts=[0,2,3,7]; c0:bw=62,experts=[0,2,3,4,6,7]; c4:bw=38,experts=[0,3,6]; c9:bw=31,experts=[0,3,6]; c1:bw=28,experts=[0,3]; c5:bw=30,experts=[0,3,4]; c2:bw=46,experts=[0,2,3,7]</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>2.6779,9.5514,1.3051,12.4048,4.2664,7.2308,3.0707,10.6388,2.2392,8.0806</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:07:44</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.5865974094764392</v>
+      </c>
+      <c r="F90" t="n">
+        <v>95.37876459741857</v>
+      </c>
+      <c r="G90" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H90" t="n">
+        <v>86</v>
+      </c>
+      <c r="I90" t="n">
+        <v>64.0681</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1:04.07</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>61.4955</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.1341</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2.4377</v>
+      </c>
+      <c r="N90" t="n">
+        <v>5709.4182</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1:35:09.42</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>3,8,2,9,7,5,0,6,4,1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>3:31;8:74;2:44;9:60;7:21;5:46;0:13;6:32;4:30;1:41</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>3:[3,5,6];8:[0,1,2,3,4,6,7];2:[2,3,4,7];9:[0,2,3,4,5,6];7:[3,6];5:[0,3,6,7];0:[5];6:[2,3,4];4:[0,2,3];1:[0,3,5,6]</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>c3:bw=31,experts=[3,5,6]; c8:bw=74,experts=[0,1,2,3,4,6,7]; c2:bw=44,experts=[2,3,4,7]; c9:bw=60,experts=[0,2,3,4,5,6]; c7:bw=21,experts=[3,6]; c5:bw=46,experts=[0,3,6,7]; c0:bw=13,experts=[5]; c6:bw=32,experts=[2,3,4]; c4:bw=30,experts=[0,2,3]; c1:bw=41,experts=[0,3,5,6]</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>1.3075,2.6948,8.0606,3.0918,12.4135,2.2458,4.1820,9.5131,7.2968,10.6896</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:08:48</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.5867533892084291</v>
+      </c>
+      <c r="F91" t="n">
+        <v>95.40181315304241</v>
+      </c>
+      <c r="G91" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H91" t="n">
+        <v>86</v>
+      </c>
+      <c r="I91" t="n">
+        <v>64.5651</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1:04.57</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>61.8736</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2.5557</v>
+      </c>
+      <c r="N91" t="n">
+        <v>5774.0172</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1:36:14.02</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>7,1,3,9,0,6,2,5,8,4</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>7:72;1:31;3:36;9:63;0:64;6:26;2:21;5:27;8:50;4:35</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>7:[0,2,3,4,5,6,7];1:[0,3,6];3:[2,3,6];9:[0,1,2,3,4,6];0:[0,2,3,5,6,7];6:[3,7];2:[2,3];5:[0,3];8:[0,3,5,6,7];4:[0,3,7]</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>c7:bw=72,experts=[0,2,3,4,5,6,7]; c1:bw=31,experts=[0,3,6]; c3:bw=36,experts=[2,3,6]; c9:bw=63,experts=[0,1,2,3,4,6]; c0:bw=64,experts=[0,2,3,5,6,7]; c6:bw=26,experts=[3,7]; c2:bw=21,experts=[2,3]; c5:bw=27,experts=[0,3]; c8:bw=50,experts=[0,3,5,6,7]; c4:bw=35,experts=[0,3,7]</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>12.6127,10.8427,1.3219,3.1240,4.3298,9.5194,7.9963,2.2504,2.6657,7.2106</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:09:52</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.5860804883103075</v>
+      </c>
+      <c r="F92" t="n">
+        <v>95.1060233558697</v>
+      </c>
+      <c r="G92" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H92" t="n">
+        <v>86</v>
+      </c>
+      <c r="I92" t="n">
+        <v>64.0077</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1:04.01</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>61.4318</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2.4392</v>
+      </c>
+      <c r="N92" t="n">
+        <v>5838.0595</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1:37:18.06</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1,9,5,7,3,4,0,6,2,8</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1:50;9:35;5:52;7:51;3:40;4:54;0:22;6:29;2:11;8:23</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1:[0,2,3,6,7];9:[0,3,7];5:[0,2,3,6,7];7:[0,2,3,4,7];3:[0,2,3,6];4:[0,2,3,6,7];0:[3,7];6:[2,3];2:[1];8:[0,3]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>c1:bw=50,experts=[0,2,3,6,7]; c9:bw=35,experts=[0,3,7]; c5:bw=52,experts=[0,2,3,6,7]; c7:bw=51,experts=[0,2,3,4,7]; c3:bw=40,experts=[0,2,3,6]; c4:bw=54,experts=[0,2,3,6,7]; c0:bw=22,experts=[3,7]; c6:bw=29,experts=[2,3]; c2:bw=11,experts=[1]; c8:bw=23,experts=[0,3]</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>10.7864,3.1109,2.2568,12.5023,1.3300,7.2798,4.2427,9.4070,7.8795,2.6364</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:10:57</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.5912990050477406</v>
+      </c>
+      <c r="F93" t="n">
+        <v>95.50553165334972</v>
+      </c>
+      <c r="G93" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H93" t="n">
+        <v>86</v>
+      </c>
+      <c r="I93" t="n">
+        <v>64.19450000000001</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>1:04.19</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>61.5695</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="M93" t="n">
+        <v>2.4926</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5902.2878</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1:38:22.29</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>3,7,1,0,8,6,9,2,5,4</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>3:28;7:34;1:20;0:29;8:19;6:45;9:56;2:25;5:66;4:26</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>3:[3,6];7:[0,3,7];1:[0,3];0:[0,3];8:[3];6:[2,3,4,5];9:[0,1,2,3,6];2:[3,6];5:[0,1,2,3,6,7];4:[0,3]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>c3:bw=28,experts=[3,6]; c7:bw=34,experts=[0,3,7]; c1:bw=20,experts=[0,3]; c0:bw=29,experts=[0,3]; c8:bw=19,experts=[3]; c6:bw=45,experts=[2,3,4,5]; c9:bw=56,experts=[0,1,2,3,6]; c2:bw=25,experts=[3,6]; c5:bw=66,experts=[0,1,2,3,6,7]; c4:bw=26,experts=[0,3]</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>1.3346,12.5336,10.7702,4.2242,2.6534,9.5271,3.1067,7.9436,2.2576,7.2184</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:12:01</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.5915846782163879</v>
+      </c>
+      <c r="F94" t="n">
+        <v>95.19821757836509</v>
+      </c>
+      <c r="G94" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H94" t="n">
+        <v>86</v>
+      </c>
+      <c r="I94" t="n">
+        <v>63.9578</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>1:03.96</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>61.3614</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="M94" t="n">
+        <v>2.4613</v>
+      </c>
+      <c r="N94" t="n">
+        <v>5966.28</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1:39:26.28</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1,3,7,9,6,8,5,4,0,2</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1:47;3:31;7:22;9:58;6:22;8:10;5:10;4:32;0:19;2:51</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1:[0,3,6,7];3:[3,4,6];7:[3,7];9:[0,1,2,3,6];6:[3,7];8:[3];5:[5];4:[0,3,7];0:[1];2:[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>c1:bw=47,experts=[0,3,6,7]; c3:bw=31,experts=[3,4,6]; c7:bw=22,experts=[3,7]; c9:bw=58,experts=[0,1,2,3,6]; c6:bw=22,experts=[3,7]; c8:bw=10,experts=[3]; c5:bw=10,experts=[5]; c4:bw=32,experts=[0,3,7]; c0:bw=19,experts=[1]; c2:bw=51,experts=[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>10.8294,1.3209,12.4159,3.1235,9.4228,2.6230,2.2048,7.2316,4.1451,8.0444</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:13:05</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.5902344874791356</v>
+      </c>
+      <c r="F95" t="n">
+        <v>95.29041180086048</v>
+      </c>
+      <c r="G95" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H95" t="n">
+        <v>86</v>
+      </c>
+      <c r="I95" t="n">
+        <v>64.6913</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>1:04.69</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>62.033</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="M95" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="N95" t="n">
+        <v>6031.0067</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1:40:31.01</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>7,2,5,4,6,9,1,8,0,3</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>7:45;2:65;5:41;4:31;6:30;9:50;1:70;8:10;0:55;3:34</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>7:[0,1,3,7];2:[0,2,3,4,6,7];5:[0,2,3,6];4:[0,2,3];6:[1,2,3];9:[0,1,2,3,6];1:[0,1,2,3,4,6,7];8:[3];0:[0,2,3,6,7];3:[0,3,6]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>c7:bw=45,experts=[0,1,3,7]; c2:bw=65,experts=[0,2,3,4,6,7]; c5:bw=41,experts=[0,2,3,6]; c4:bw=31,experts=[0,2,3]; c6:bw=30,experts=[1,2,3]; c9:bw=50,experts=[0,1,2,3,6]; c1:bw=70,experts=[0,1,2,3,4,6,7]; c8:bw=10,experts=[3]; c0:bw=55,experts=[0,2,3,6,7]; c3:bw=34,experts=[0,3,6]</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>12.6354,8.1199,2.2692,7.2927,9.4791,3.1098,10.8671,2.6706,4.2654,1.3237</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:14:10</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.5915122571862621</v>
+      </c>
+      <c r="F96" t="n">
+        <v>95.2519975414874</v>
+      </c>
+      <c r="G96" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H96" t="n">
+        <v>86</v>
+      </c>
+      <c r="I96" t="n">
+        <v>64.1965</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>1:04.20</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>61.5814</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.1283</v>
+      </c>
+      <c r="M96" t="n">
+        <v>2.4823</v>
+      </c>
+      <c r="N96" t="n">
+        <v>6095.2397</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1:41:35.24</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>7,9,4,6,0,3,1,8,2,5</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>7:59;9:42;4:15;6:40;0:35;3:41;1:31;8:76;2:23;5:10</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>7:[0,2,3,4,7];9:[0,2,3,6];4:[1];6:[0,3,5,7];0:[0,3,7];3:[1,3,6,7];1:[0,3,6];8:[0,2,3,4,5,6,7];2:[3,5];5:[3]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>c7:bw=59,experts=[0,2,3,4,7]; c9:bw=42,experts=[0,2,3,6]; c4:bw=15,experts=[1]; c6:bw=40,experts=[0,3,5,7]; c0:bw=35,experts=[0,3,7]; c3:bw=41,experts=[1,3,6,7]; c1:bw=31,experts=[0,3,6]; c8:bw=76,experts=[0,2,3,4,5,6,7]; c2:bw=23,experts=[3,5]; c5:bw=10,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>12.5505,3.0821,7.1841,9.4579,4.2578,1.3226,10.7742,2.7205,7.9965,2.2352</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:15:14</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.5886720243171722</v>
+      </c>
+      <c r="F97" t="n">
+        <v>95.49400737553781</v>
+      </c>
+      <c r="G97" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H97" t="n">
+        <v>86</v>
+      </c>
+      <c r="I97" t="n">
+        <v>64.2758</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>1:04.28</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>61.7053</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="M97" t="n">
+        <v>2.4405</v>
+      </c>
+      <c r="N97" t="n">
+        <v>6159.5513</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1:42:39.55</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2,9,3,1,5,4,6,7,0,8</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2:65;9:44;3:46;1:36;5:60;4:49;6:31;7:50;0:36;8:64</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>2:[0,2,3,4,6,7];9:[0,2,3,6];3:[1,2,3,6];1:[0,3,6];5:[0,2,3,4,6,7];4:[0,3,4,5];6:[2,3,6];7:[0,2,3,4,7];0:[0,3,4];8:[0,1,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>c2:bw=65,experts=[0,2,3,4,6,7]; c9:bw=44,experts=[0,2,3,6]; c3:bw=46,experts=[1,2,3,6]; c1:bw=36,experts=[0,3,6]; c5:bw=60,experts=[0,2,3,4,6,7]; c4:bw=49,experts=[0,3,4,5]; c6:bw=31,experts=[2,3,6]; c7:bw=50,experts=[0,2,3,4,7]; c0:bw=36,experts=[0,3,4]; c8:bw=64,experts=[0,1,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>8.1113,3.1271,1.3229,10.7774,2.2548,7.2634,9.4416,12.4358,4.2812,2.6897</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:16:19</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.5830338300494122</v>
+      </c>
+      <c r="F98" t="n">
+        <v>95.24047326367548</v>
+      </c>
+      <c r="G98" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H98" t="n">
+        <v>86</v>
+      </c>
+      <c r="I98" t="n">
+        <v>64.60299999999999</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1:04.60</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>61.9594</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.1329</v>
+      </c>
+      <c r="M98" t="n">
+        <v>2.5077</v>
+      </c>
+      <c r="N98" t="n">
+        <v>6224.1904</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1:43:44.19</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>0,9,8,4,7,1,3,5,6,2</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>0:41;9:43;8:43;4:16;7:30;1:50;3:35;5:46;6:50;2:54</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>0:[0,2,3,7];9:[0,3,5,6];8:[0,2,3,6];4:[3];7:[0,3,7];1:[0,2,3,5,6];3:[3,5,6];5:[0,2,3,7];6:[0,2,3,5,7];2:[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>c0:bw=41,experts=[0,2,3,7]; c9:bw=43,experts=[0,3,5,6]; c8:bw=43,experts=[0,2,3,6]; c4:bw=16,experts=[3]; c7:bw=30,experts=[0,3,7]; c1:bw=50,experts=[0,2,3,5,6]; c3:bw=35,experts=[3,5,6]; c5:bw=46,experts=[0,2,3,7]; c6:bw=50,experts=[0,2,3,5,7]; c2:bw=54,experts=[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>4.3240,3.1114,2.6935,7.2140,12.5361,10.9115,1.3164,2.2658,9.5450,8.0416</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:17:23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.5824802700800418</v>
+      </c>
+      <c r="F99" t="n">
+        <v>95.50553165334972</v>
+      </c>
+      <c r="G99" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H99" t="n">
+        <v>86</v>
+      </c>
+      <c r="I99" t="n">
+        <v>63.9673</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>1:03.97</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>61.3297</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2.4989</v>
+      </c>
+      <c r="N99" t="n">
+        <v>6288.1945</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1:44:48.19</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>4,8,9,7,6,5,0,3,1,2</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>4:52;8:54;9:27;7:24;6:36;5:49;0:33;3:25;1:26;2:24</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>4:[0,2,3,6,7];8:[0,2,3,6,7];9:[3,4];7:[5,6];6:[2,3,5];5:[0,2,3,6];0:[0,3,5];3:[3,6];1:[0,3];2:[2,3]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>c4:bw=52,experts=[0,2,3,6,7]; c8:bw=54,experts=[0,2,3,6,7]; c9:bw=27,experts=[3,4]; c7:bw=24,experts=[5,6]; c6:bw=36,experts=[2,3,5]; c5:bw=49,experts=[0,2,3,6]; c0:bw=33,experts=[0,3,5]; c3:bw=25,experts=[3,6]; c1:bw=26,experts=[0,3]; c2:bw=24,experts=[2,3]</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>7.3030,2.7148,3.0875,12.2290,9.5568,2.2685,4.2257,1.3019,10.6879,7.9547</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:18:27</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.5942526927627093</v>
+      </c>
+      <c r="F100" t="n">
+        <v>95.28272894898586</v>
+      </c>
+      <c r="G100" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H100" t="n">
+        <v>86</v>
+      </c>
+      <c r="I100" t="n">
+        <v>64.39749999999999</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1:04.40</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>61.7445</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.1351</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2.5143</v>
+      </c>
+      <c r="N100" t="n">
+        <v>6352.6296</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1:45:52.63</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>8,5,7,1,3,9,4,0,2,6</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>8:34;5:49;7:45;1:59;3:38;9:20;4:24;0:40;2:31;6:35</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>8:[0,3,6];5:[0,2,3,6];7:[0,3,4,7];1:[0,2,3,6,7];3:[2,3,6];9:[3,7];4:[0,3];0:[0,3,6,7];2:[1,2,3];6:[2,3,5]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>c8:bw=34,experts=[0,3,6]; c5:bw=49,experts=[0,2,3,6]; c7:bw=45,experts=[0,3,4,7]; c1:bw=59,experts=[0,2,3,6,7]; c3:bw=38,experts=[2,3,6]; c9:bw=20,experts=[3,7]; c4:bw=24,experts=[0,3]; c0:bw=40,experts=[0,3,6,7]; c2:bw=31,experts=[1,2,3]; c6:bw=35,experts=[2,3,5]</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>2.6972,2.2795,12.5333,10.8832,1.3037,3.0893,7.2610,4.2784,7.9668,9.4522</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:19:31</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.5896877049945481</v>
+      </c>
+      <c r="F101" t="n">
+        <v>95.31730178242164</v>
+      </c>
+      <c r="G101" t="n">
+        <v>95.56315304240934</v>
+      </c>
+      <c r="H101" t="n">
+        <v>86</v>
+      </c>
+      <c r="I101" t="n">
+        <v>64.2666</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1:04.27</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>61.6817</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="M101" t="n">
+        <v>2.4552</v>
+      </c>
+      <c r="N101" t="n">
+        <v>6416.9334</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1:46:56.93</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2,8,9,5,6,1,4,7,3,0</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2:30;8:44;9:53;5:18;6:44;1:17;4:65;7:10;3:42;0:64</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>2:[2,3,7];8:[0,2,3,6];9:[0,1,2,3,6];5:[1];6:[3,4,5,7];1:[3];4:[0,1,2,3,6,7];7:[3];3:[0,2,3,6];0:[0,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>c2:bw=30,experts=[2,3,7]; c8:bw=44,experts=[0,2,3,6]; c9:bw=53,experts=[0,1,2,3,6]; c5:bw=18,experts=[1]; c6:bw=44,experts=[3,4,5,7]; c1:bw=17,experts=[3]; c4:bw=65,experts=[0,1,2,3,6,7]; c7:bw=10,experts=[3]; c3:bw=42,experts=[0,2,3,6]; c0:bw=64,experts=[0,2,3,4,6,7]</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>8.0699,2.7216,3.1306,2.2167,9.5043,10.7167,7.3317,12.3753,1.3040,4.3108</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
